--- a/output/version3/test/25-15/MARL/IL/RL-RL (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/25-15/MARL/IL/RL-RL (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1057</v>
+        <v>998</v>
       </c>
       <c r="C2" t="n">
-        <v>1090</v>
+        <v>1030</v>
       </c>
       <c r="D2" t="n">
-        <v>1073</v>
+        <v>1022</v>
       </c>
       <c r="E2" t="n">
-        <v>1245</v>
+        <v>1074</v>
       </c>
       <c r="F2" t="n">
-        <v>1146</v>
+        <v>1176</v>
       </c>
       <c r="G2" t="n">
-        <v>1258</v>
+        <v>1019</v>
       </c>
       <c r="H2" t="n">
-        <v>997</v>
+        <v>1147</v>
       </c>
       <c r="I2" t="n">
-        <v>1095</v>
+        <v>1075</v>
       </c>
       <c r="J2" t="n">
-        <v>1085</v>
+        <v>1134</v>
       </c>
       <c r="K2" t="n">
-        <v>1202</v>
+        <v>1128</v>
       </c>
       <c r="L2" t="n">
-        <v>1124.8</v>
+        <v>1080.3</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1081</v>
+        <v>1048</v>
       </c>
       <c r="C3" t="n">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D3" t="n">
-        <v>1169</v>
+        <v>1029</v>
       </c>
       <c r="E3" t="n">
-        <v>1015</v>
+        <v>966</v>
       </c>
       <c r="F3" t="n">
-        <v>1119</v>
+        <v>1173</v>
       </c>
       <c r="G3" t="n">
-        <v>1193</v>
+        <v>1168</v>
       </c>
       <c r="H3" t="n">
-        <v>1177</v>
+        <v>1124</v>
       </c>
       <c r="I3" t="n">
-        <v>1056</v>
+        <v>1111</v>
       </c>
       <c r="J3" t="n">
-        <v>1194</v>
+        <v>1041</v>
       </c>
       <c r="K3" t="n">
-        <v>1040</v>
+        <v>1234</v>
       </c>
       <c r="L3" t="n">
-        <v>1115.1</v>
+        <v>1100.2</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>1142</v>
+        <v>1116</v>
       </c>
       <c r="C4" t="n">
-        <v>1271</v>
+        <v>1063</v>
       </c>
       <c r="D4" t="n">
-        <v>1142</v>
+        <v>1044</v>
       </c>
       <c r="E4" t="n">
-        <v>1045</v>
+        <v>1175</v>
       </c>
       <c r="F4" t="n">
-        <v>1109</v>
+        <v>992</v>
       </c>
       <c r="G4" t="n">
-        <v>1091</v>
+        <v>1058</v>
       </c>
       <c r="H4" t="n">
-        <v>1165</v>
+        <v>1015</v>
       </c>
       <c r="I4" t="n">
-        <v>969</v>
+        <v>1097</v>
       </c>
       <c r="J4" t="n">
-        <v>1011</v>
+        <v>1137</v>
       </c>
       <c r="K4" t="n">
-        <v>1111</v>
+        <v>1181</v>
       </c>
       <c r="L4" t="n">
-        <v>1105.6</v>
+        <v>1087.8</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>946</v>
+        <v>838</v>
       </c>
       <c r="C5" t="n">
-        <v>1027</v>
+        <v>890</v>
       </c>
       <c r="D5" t="n">
-        <v>1221</v>
+        <v>913</v>
       </c>
       <c r="E5" t="n">
-        <v>1115</v>
+        <v>904</v>
       </c>
       <c r="F5" t="n">
-        <v>938</v>
+        <v>1043</v>
       </c>
       <c r="G5" t="n">
-        <v>937</v>
+        <v>919</v>
       </c>
       <c r="H5" t="n">
-        <v>870</v>
+        <v>972</v>
       </c>
       <c r="I5" t="n">
-        <v>942</v>
+        <v>1082</v>
       </c>
       <c r="J5" t="n">
-        <v>1016</v>
+        <v>858</v>
       </c>
       <c r="K5" t="n">
-        <v>863</v>
+        <v>1035</v>
       </c>
       <c r="L5" t="n">
-        <v>987.5</v>
+        <v>945.4</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1143</v>
+        <v>1028</v>
       </c>
       <c r="C6" t="n">
-        <v>1093</v>
+        <v>989</v>
       </c>
       <c r="D6" t="n">
-        <v>1076</v>
+        <v>960</v>
       </c>
       <c r="E6" t="n">
-        <v>1181</v>
+        <v>1070</v>
       </c>
       <c r="F6" t="n">
-        <v>1112</v>
+        <v>1038</v>
       </c>
       <c r="G6" t="n">
-        <v>1019</v>
+        <v>1006</v>
       </c>
       <c r="H6" t="n">
-        <v>1009</v>
+        <v>1102</v>
       </c>
       <c r="I6" t="n">
-        <v>1136</v>
+        <v>980</v>
       </c>
       <c r="J6" t="n">
-        <v>1055</v>
+        <v>997</v>
       </c>
       <c r="K6" t="n">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="L6" t="n">
-        <v>1100.4</v>
+        <v>1034.4</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>990</v>
+        <v>1153</v>
       </c>
       <c r="C7" t="n">
-        <v>1081</v>
+        <v>1038</v>
       </c>
       <c r="D7" t="n">
-        <v>994</v>
+        <v>1111</v>
       </c>
       <c r="E7" t="n">
-        <v>935</v>
+        <v>1052</v>
       </c>
       <c r="F7" t="n">
-        <v>1196</v>
+        <v>974</v>
       </c>
       <c r="G7" t="n">
-        <v>1158</v>
+        <v>1027</v>
       </c>
       <c r="H7" t="n">
-        <v>1071</v>
+        <v>1123</v>
       </c>
       <c r="I7" t="n">
-        <v>1016</v>
+        <v>1073</v>
       </c>
       <c r="J7" t="n">
-        <v>1059</v>
+        <v>963</v>
       </c>
       <c r="K7" t="n">
-        <v>936</v>
+        <v>958</v>
       </c>
       <c r="L7" t="n">
-        <v>1043.6</v>
+        <v>1047.2</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>943</v>
+        <v>968</v>
       </c>
       <c r="C8" t="n">
-        <v>992</v>
+        <v>1139</v>
       </c>
       <c r="D8" t="n">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="E8" t="n">
-        <v>1051</v>
+        <v>930</v>
       </c>
       <c r="F8" t="n">
-        <v>1086</v>
+        <v>993</v>
       </c>
       <c r="G8" t="n">
-        <v>1011</v>
+        <v>994</v>
       </c>
       <c r="H8" t="n">
-        <v>1078</v>
+        <v>1006</v>
       </c>
       <c r="I8" t="n">
-        <v>998</v>
+        <v>1050</v>
       </c>
       <c r="J8" t="n">
-        <v>884</v>
+        <v>1142</v>
       </c>
       <c r="K8" t="n">
-        <v>1037</v>
+        <v>965</v>
       </c>
       <c r="L8" t="n">
-        <v>1012.3</v>
+        <v>1022.7</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>983</v>
+        <v>968</v>
       </c>
       <c r="C9" t="n">
-        <v>1063</v>
+        <v>901</v>
       </c>
       <c r="D9" t="n">
-        <v>1008</v>
+        <v>985</v>
       </c>
       <c r="E9" t="n">
-        <v>984</v>
+        <v>936</v>
       </c>
       <c r="F9" t="n">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="G9" t="n">
-        <v>1012</v>
+        <v>1121</v>
       </c>
       <c r="H9" t="n">
-        <v>911</v>
+        <v>1080</v>
       </c>
       <c r="I9" t="n">
-        <v>1044</v>
+        <v>924</v>
       </c>
       <c r="J9" t="n">
-        <v>1142</v>
+        <v>1075</v>
       </c>
       <c r="K9" t="n">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="L9" t="n">
-        <v>1001</v>
+        <v>983.7</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>962</v>
+        <v>1147</v>
       </c>
       <c r="C10" t="n">
-        <v>1095</v>
+        <v>1173</v>
       </c>
       <c r="D10" t="n">
-        <v>1001</v>
+        <v>1098</v>
       </c>
       <c r="E10" t="n">
-        <v>1107</v>
+        <v>1139</v>
       </c>
       <c r="F10" t="n">
-        <v>1233</v>
+        <v>1085</v>
       </c>
       <c r="G10" t="n">
-        <v>1225</v>
+        <v>1138</v>
       </c>
       <c r="H10" t="n">
-        <v>1040</v>
+        <v>1154</v>
       </c>
       <c r="I10" t="n">
-        <v>1067</v>
+        <v>921</v>
       </c>
       <c r="J10" t="n">
-        <v>1042</v>
+        <v>972</v>
       </c>
       <c r="K10" t="n">
-        <v>940</v>
+        <v>1059</v>
       </c>
       <c r="L10" t="n">
-        <v>1071.2</v>
+        <v>1088.6</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1043</v>
+        <v>1167</v>
       </c>
       <c r="C11" t="n">
-        <v>965</v>
+        <v>1030</v>
       </c>
       <c r="D11" t="n">
-        <v>894</v>
+        <v>1149</v>
       </c>
       <c r="E11" t="n">
-        <v>1014</v>
+        <v>975</v>
       </c>
       <c r="F11" t="n">
-        <v>990</v>
+        <v>1125</v>
       </c>
       <c r="G11" t="n">
-        <v>1073</v>
+        <v>1090</v>
       </c>
       <c r="H11" t="n">
-        <v>1160</v>
+        <v>1219</v>
       </c>
       <c r="I11" t="n">
-        <v>1072</v>
+        <v>973</v>
       </c>
       <c r="J11" t="n">
-        <v>1113</v>
+        <v>1099</v>
       </c>
       <c r="K11" t="n">
-        <v>978</v>
+        <v>1122</v>
       </c>
       <c r="L11" t="n">
-        <v>1030.2</v>
+        <v>1094.9</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1073</v>
+        <v>1246</v>
       </c>
       <c r="C12" t="n">
-        <v>1291</v>
+        <v>1105</v>
       </c>
       <c r="D12" t="n">
-        <v>1170</v>
+        <v>1156</v>
       </c>
       <c r="E12" t="n">
-        <v>1282</v>
+        <v>969</v>
       </c>
       <c r="F12" t="n">
-        <v>1217</v>
+        <v>1258</v>
       </c>
       <c r="G12" t="n">
-        <v>1240</v>
+        <v>1210</v>
       </c>
       <c r="H12" t="n">
-        <v>1205</v>
+        <v>1280</v>
       </c>
       <c r="I12" t="n">
-        <v>1238</v>
+        <v>1160</v>
       </c>
       <c r="J12" t="n">
-        <v>1107</v>
+        <v>1117</v>
       </c>
       <c r="K12" t="n">
-        <v>1143</v>
+        <v>1244</v>
       </c>
       <c r="L12" t="n">
-        <v>1196.6</v>
+        <v>1174.5</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>1251</v>
+        <v>1246</v>
       </c>
       <c r="C13" t="n">
-        <v>1217</v>
+        <v>1088</v>
       </c>
       <c r="D13" t="n">
-        <v>1353</v>
+        <v>1212</v>
       </c>
       <c r="E13" t="n">
-        <v>1223</v>
+        <v>1303</v>
       </c>
       <c r="F13" t="n">
-        <v>1178</v>
+        <v>1272</v>
       </c>
       <c r="G13" t="n">
-        <v>1130</v>
+        <v>1156</v>
       </c>
       <c r="H13" t="n">
-        <v>1278</v>
+        <v>1384</v>
       </c>
       <c r="I13" t="n">
-        <v>1297</v>
+        <v>1347</v>
       </c>
       <c r="J13" t="n">
-        <v>1327</v>
+        <v>1069</v>
       </c>
       <c r="K13" t="n">
-        <v>1166</v>
+        <v>1264</v>
       </c>
       <c r="L13" t="n">
-        <v>1242</v>
+        <v>1234.1</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>1058</v>
+        <v>988</v>
       </c>
       <c r="C14" t="n">
-        <v>1059</v>
+        <v>1051</v>
       </c>
       <c r="D14" t="n">
-        <v>1033</v>
+        <v>999</v>
       </c>
       <c r="E14" t="n">
-        <v>1196</v>
+        <v>898</v>
       </c>
       <c r="F14" t="n">
-        <v>1049</v>
+        <v>1180</v>
       </c>
       <c r="G14" t="n">
-        <v>1101</v>
+        <v>1023</v>
       </c>
       <c r="H14" t="n">
-        <v>996</v>
+        <v>924</v>
       </c>
       <c r="I14" t="n">
-        <v>952</v>
+        <v>1031</v>
       </c>
       <c r="J14" t="n">
-        <v>997</v>
+        <v>1025</v>
       </c>
       <c r="K14" t="n">
-        <v>1021</v>
+        <v>1088</v>
       </c>
       <c r="L14" t="n">
-        <v>1046.2</v>
+        <v>1020.7</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1110</v>
+        <v>1029</v>
       </c>
       <c r="C15" t="n">
-        <v>1114</v>
+        <v>1047</v>
       </c>
       <c r="D15" t="n">
-        <v>1049</v>
+        <v>1068</v>
       </c>
       <c r="E15" t="n">
-        <v>1087</v>
+        <v>950</v>
       </c>
       <c r="F15" t="n">
-        <v>974</v>
+        <v>1105</v>
       </c>
       <c r="G15" t="n">
-        <v>1002</v>
+        <v>1190</v>
       </c>
       <c r="H15" t="n">
-        <v>1139</v>
+        <v>1059</v>
       </c>
       <c r="I15" t="n">
+        <v>1117</v>
+      </c>
+      <c r="J15" t="n">
         <v>1081</v>
       </c>
-      <c r="J15" t="n">
-        <v>1097</v>
-      </c>
       <c r="K15" t="n">
-        <v>1107</v>
+        <v>1056</v>
       </c>
       <c r="L15" t="n">
-        <v>1076</v>
+        <v>1070.2</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>975</v>
+        <v>1039</v>
       </c>
       <c r="C16" t="n">
-        <v>1009</v>
+        <v>1092</v>
       </c>
       <c r="D16" t="n">
-        <v>1202</v>
+        <v>946</v>
       </c>
       <c r="E16" t="n">
-        <v>1052</v>
+        <v>1251</v>
       </c>
       <c r="F16" t="n">
-        <v>1246</v>
+        <v>1098</v>
       </c>
       <c r="G16" t="n">
-        <v>1137</v>
+        <v>900</v>
       </c>
       <c r="H16" t="n">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="I16" t="n">
-        <v>1101</v>
+        <v>1131</v>
       </c>
       <c r="J16" t="n">
-        <v>1320</v>
+        <v>1079</v>
       </c>
       <c r="K16" t="n">
-        <v>1036</v>
+        <v>1309</v>
       </c>
       <c r="L16" t="n">
-        <v>1115.2</v>
+        <v>1091.3</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>1006</v>
+        <v>1047</v>
       </c>
       <c r="C17" t="n">
-        <v>1003</v>
+        <v>1249</v>
       </c>
       <c r="D17" t="n">
-        <v>1220</v>
+        <v>1015</v>
       </c>
       <c r="E17" t="n">
-        <v>1002</v>
+        <v>1087</v>
       </c>
       <c r="F17" t="n">
-        <v>987</v>
+        <v>946</v>
       </c>
       <c r="G17" t="n">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H17" t="n">
-        <v>1138</v>
+        <v>1107</v>
       </c>
       <c r="I17" t="n">
-        <v>1004</v>
+        <v>1051</v>
       </c>
       <c r="J17" t="n">
-        <v>1078</v>
+        <v>1017</v>
       </c>
       <c r="K17" t="n">
-        <v>1113</v>
+        <v>1283</v>
       </c>
       <c r="L17" t="n">
-        <v>1057</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
+        <v>1140</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1230</v>
+      </c>
+      <c r="D18" t="n">
+        <v>967</v>
+      </c>
+      <c r="E18" t="n">
         <v>1134</v>
       </c>
-      <c r="C18" t="n">
-        <v>1222</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1002</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1139</v>
-      </c>
       <c r="F18" t="n">
-        <v>1125</v>
+        <v>1070</v>
       </c>
       <c r="G18" t="n">
-        <v>1147</v>
+        <v>1122</v>
       </c>
       <c r="H18" t="n">
-        <v>1094</v>
+        <v>963</v>
       </c>
       <c r="I18" t="n">
-        <v>1174</v>
+        <v>937</v>
       </c>
       <c r="J18" t="n">
-        <v>1007</v>
+        <v>977</v>
       </c>
       <c r="K18" t="n">
-        <v>1028</v>
+        <v>1014</v>
       </c>
       <c r="L18" t="n">
-        <v>1107.2</v>
+        <v>1055.4</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>1272</v>
+        <v>1070</v>
       </c>
       <c r="C19" t="n">
-        <v>1322</v>
+        <v>1316</v>
       </c>
       <c r="D19" t="n">
-        <v>1035</v>
+        <v>971</v>
       </c>
       <c r="E19" t="n">
-        <v>1160</v>
+        <v>1005</v>
       </c>
       <c r="F19" t="n">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="G19" t="n">
-        <v>1230</v>
+        <v>1125</v>
       </c>
       <c r="H19" t="n">
-        <v>1030</v>
+        <v>1003</v>
       </c>
       <c r="I19" t="n">
-        <v>1106</v>
+        <v>1276</v>
       </c>
       <c r="J19" t="n">
-        <v>1253</v>
+        <v>1169</v>
       </c>
       <c r="K19" t="n">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="L19" t="n">
-        <v>1158.1</v>
+        <v>1111.3</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1153</v>
+        <v>1034</v>
       </c>
       <c r="C20" t="n">
-        <v>1178</v>
+        <v>1001</v>
       </c>
       <c r="D20" t="n">
-        <v>1179</v>
+        <v>1246</v>
       </c>
       <c r="E20" t="n">
-        <v>1103</v>
+        <v>1084</v>
       </c>
       <c r="F20" t="n">
+        <v>1221</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1118</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1191</v>
+      </c>
+      <c r="I20" t="n">
         <v>1150</v>
       </c>
-      <c r="G20" t="n">
-        <v>1280</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1206</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1229</v>
-      </c>
       <c r="J20" t="n">
-        <v>1015</v>
+        <v>1038</v>
       </c>
       <c r="K20" t="n">
-        <v>1233</v>
+        <v>1328</v>
       </c>
       <c r="L20" t="n">
-        <v>1172.6</v>
+        <v>1141.1</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>988</v>
+        <v>1116</v>
       </c>
       <c r="C21" t="n">
-        <v>1130</v>
+        <v>1195</v>
       </c>
       <c r="D21" t="n">
+        <v>1134</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G21" t="n">
         <v>1064</v>
       </c>
-      <c r="E21" t="n">
-        <v>1134</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1208</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1050</v>
-      </c>
       <c r="H21" t="n">
-        <v>1078</v>
+        <v>1126</v>
       </c>
       <c r="I21" t="n">
-        <v>1182</v>
+        <v>1041</v>
       </c>
       <c r="J21" t="n">
-        <v>1091</v>
+        <v>1055</v>
       </c>
       <c r="K21" t="n">
-        <v>1313</v>
+        <v>1016</v>
       </c>
       <c r="L21" t="n">
-        <v>1123.8</v>
+        <v>1100.7</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>1226</v>
+        <v>1007</v>
       </c>
       <c r="C22" t="n">
-        <v>1217</v>
+        <v>1171</v>
       </c>
       <c r="D22" t="n">
-        <v>1273</v>
+        <v>1090</v>
       </c>
       <c r="E22" t="n">
-        <v>1261</v>
+        <v>1086</v>
       </c>
       <c r="F22" t="n">
-        <v>1087</v>
+        <v>1059</v>
       </c>
       <c r="G22" t="n">
-        <v>1191</v>
+        <v>1186</v>
       </c>
       <c r="H22" t="n">
-        <v>1182</v>
+        <v>1018</v>
       </c>
       <c r="I22" t="n">
-        <v>1046</v>
+        <v>1339</v>
       </c>
       <c r="J22" t="n">
-        <v>1015</v>
+        <v>944</v>
       </c>
       <c r="K22" t="n">
-        <v>1171</v>
+        <v>1071</v>
       </c>
       <c r="L22" t="n">
-        <v>1166.9</v>
+        <v>1097.1</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>902</v>
+        <v>881</v>
       </c>
       <c r="C23" t="n">
+        <v>995</v>
+      </c>
+      <c r="D23" t="n">
+        <v>894</v>
+      </c>
+      <c r="E23" t="n">
         <v>1010</v>
       </c>
-      <c r="D23" t="n">
-        <v>850</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1094</v>
-      </c>
       <c r="F23" t="n">
-        <v>977</v>
+        <v>1049</v>
       </c>
       <c r="G23" t="n">
-        <v>948</v>
+        <v>1028</v>
       </c>
       <c r="H23" t="n">
-        <v>1027</v>
+        <v>986</v>
       </c>
       <c r="I23" t="n">
-        <v>1048</v>
+        <v>988</v>
       </c>
       <c r="J23" t="n">
-        <v>1024</v>
+        <v>935</v>
       </c>
       <c r="K23" t="n">
-        <v>1012</v>
+        <v>1193</v>
       </c>
       <c r="L23" t="n">
-        <v>989.2</v>
+        <v>995.9</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>969</v>
+        <v>1062</v>
       </c>
       <c r="C24" t="n">
-        <v>1013</v>
+        <v>1096</v>
       </c>
       <c r="D24" t="n">
-        <v>1114</v>
+        <v>1153</v>
       </c>
       <c r="E24" t="n">
-        <v>1009</v>
+        <v>1126</v>
       </c>
       <c r="F24" t="n">
-        <v>993</v>
+        <v>1157</v>
       </c>
       <c r="G24" t="n">
-        <v>1113</v>
+        <v>1021</v>
       </c>
       <c r="H24" t="n">
-        <v>1010</v>
+        <v>1132</v>
       </c>
       <c r="I24" t="n">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="J24" t="n">
-        <v>1103</v>
+        <v>1055</v>
       </c>
       <c r="K24" t="n">
-        <v>1096</v>
+        <v>1068</v>
       </c>
       <c r="L24" t="n">
-        <v>1052.5</v>
+        <v>1097.1</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1068</v>
+        <v>1029</v>
       </c>
       <c r="C25" t="n">
-        <v>1186</v>
+        <v>1126</v>
       </c>
       <c r="D25" t="n">
-        <v>954</v>
+        <v>1272</v>
       </c>
       <c r="E25" t="n">
-        <v>1287</v>
+        <v>1224</v>
       </c>
       <c r="F25" t="n">
-        <v>1112</v>
+        <v>1303</v>
       </c>
       <c r="G25" t="n">
-        <v>1149</v>
+        <v>1128</v>
       </c>
       <c r="H25" t="n">
-        <v>1169</v>
+        <v>1021</v>
       </c>
       <c r="I25" t="n">
-        <v>1041</v>
+        <v>1143</v>
       </c>
       <c r="J25" t="n">
         <v>1121</v>
       </c>
       <c r="K25" t="n">
-        <v>1177</v>
+        <v>1221</v>
       </c>
       <c r="L25" t="n">
-        <v>1126.4</v>
+        <v>1158.8</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>957</v>
+        <v>918</v>
       </c>
       <c r="C26" t="n">
-        <v>975</v>
+        <v>1070</v>
       </c>
       <c r="D26" t="n">
-        <v>960</v>
+        <v>1128</v>
       </c>
       <c r="E26" t="n">
-        <v>1083</v>
+        <v>1139</v>
       </c>
       <c r="F26" t="n">
-        <v>967</v>
+        <v>1016</v>
       </c>
       <c r="G26" t="n">
-        <v>1021</v>
+        <v>985</v>
       </c>
       <c r="H26" t="n">
-        <v>1070</v>
+        <v>934</v>
       </c>
       <c r="I26" t="n">
-        <v>1057</v>
+        <v>1002</v>
       </c>
       <c r="J26" t="n">
-        <v>953</v>
+        <v>1095</v>
       </c>
       <c r="K26" t="n">
-        <v>1072</v>
+        <v>997</v>
       </c>
       <c r="L26" t="n">
-        <v>1011.5</v>
+        <v>1028.4</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1218</v>
+        <v>1019</v>
       </c>
       <c r="C27" t="n">
-        <v>1083</v>
+        <v>1210</v>
       </c>
       <c r="D27" t="n">
-        <v>1070</v>
+        <v>1160</v>
       </c>
       <c r="E27" t="n">
-        <v>1208</v>
+        <v>1176</v>
       </c>
       <c r="F27" t="n">
-        <v>1272</v>
+        <v>1033</v>
       </c>
       <c r="G27" t="n">
-        <v>1115</v>
+        <v>1077</v>
       </c>
       <c r="H27" t="n">
-        <v>945</v>
+        <v>1158</v>
       </c>
       <c r="I27" t="n">
-        <v>1180</v>
+        <v>1071</v>
       </c>
       <c r="J27" t="n">
-        <v>1206</v>
+        <v>1145</v>
       </c>
       <c r="K27" t="n">
-        <v>1292</v>
+        <v>1202</v>
       </c>
       <c r="L27" t="n">
-        <v>1158.9</v>
+        <v>1125.1</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1092</v>
+        <v>1056</v>
       </c>
       <c r="C28" t="n">
-        <v>1064</v>
+        <v>1078</v>
       </c>
       <c r="D28" t="n">
-        <v>1173</v>
+        <v>1117</v>
       </c>
       <c r="E28" t="n">
-        <v>1047</v>
+        <v>1210</v>
       </c>
       <c r="F28" t="n">
-        <v>1224</v>
+        <v>1150</v>
       </c>
       <c r="G28" t="n">
-        <v>1003</v>
+        <v>1025</v>
       </c>
       <c r="H28" t="n">
-        <v>1135</v>
+        <v>962</v>
       </c>
       <c r="I28" t="n">
-        <v>1078</v>
+        <v>1036</v>
       </c>
       <c r="J28" t="n">
-        <v>1023</v>
+        <v>927</v>
       </c>
       <c r="K28" t="n">
-        <v>1126</v>
+        <v>939</v>
       </c>
       <c r="L28" t="n">
-        <v>1096.5</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>1145</v>
+        <v>975</v>
       </c>
       <c r="C29" t="n">
-        <v>1167</v>
+        <v>1111</v>
       </c>
       <c r="D29" t="n">
-        <v>1156</v>
+        <v>938</v>
       </c>
       <c r="E29" t="n">
-        <v>977</v>
+        <v>917</v>
       </c>
       <c r="F29" t="n">
-        <v>1100</v>
+        <v>1050</v>
       </c>
       <c r="G29" t="n">
-        <v>1259</v>
+        <v>1149</v>
       </c>
       <c r="H29" t="n">
-        <v>1210</v>
+        <v>999</v>
       </c>
       <c r="I29" t="n">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="J29" t="n">
-        <v>1010</v>
+        <v>1044</v>
       </c>
       <c r="K29" t="n">
-        <v>1144</v>
+        <v>804</v>
       </c>
       <c r="L29" t="n">
-        <v>1119.6</v>
+        <v>1002.1</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>1097</v>
+        <v>1016</v>
       </c>
       <c r="C30" t="n">
-        <v>1047</v>
+        <v>1163</v>
       </c>
       <c r="D30" t="n">
-        <v>1017</v>
+        <v>1149</v>
       </c>
       <c r="E30" t="n">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="F30" t="n">
-        <v>1070</v>
+        <v>1033</v>
       </c>
       <c r="G30" t="n">
-        <v>1027</v>
+        <v>1174</v>
       </c>
       <c r="H30" t="n">
-        <v>1107</v>
+        <v>1029</v>
       </c>
       <c r="I30" t="n">
-        <v>1056</v>
+        <v>1065</v>
       </c>
       <c r="J30" t="n">
-        <v>923</v>
+        <v>1156</v>
       </c>
       <c r="K30" t="n">
-        <v>1104</v>
+        <v>1039</v>
       </c>
       <c r="L30" t="n">
-        <v>1052.8</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1010</v>
+        <v>1332</v>
       </c>
       <c r="C31" t="n">
-        <v>1191</v>
+        <v>1030</v>
       </c>
       <c r="D31" t="n">
-        <v>1013</v>
+        <v>1264</v>
       </c>
       <c r="E31" t="n">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="F31" t="n">
-        <v>1179</v>
+        <v>1267</v>
       </c>
       <c r="G31" t="n">
-        <v>952</v>
+        <v>1293</v>
       </c>
       <c r="H31" t="n">
-        <v>1186</v>
+        <v>1296</v>
       </c>
       <c r="I31" t="n">
-        <v>1347</v>
+        <v>1184</v>
       </c>
       <c r="J31" t="n">
-        <v>1234</v>
+        <v>1095</v>
       </c>
       <c r="K31" t="n">
-        <v>1140</v>
+        <v>1271</v>
       </c>
       <c r="L31" t="n">
-        <v>1135</v>
+        <v>1212.5</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>892</v>
+        <v>985</v>
       </c>
       <c r="C32" t="n">
-        <v>948</v>
+        <v>1050</v>
       </c>
       <c r="D32" t="n">
-        <v>919</v>
+        <v>1057</v>
       </c>
       <c r="E32" t="n">
-        <v>1067</v>
+        <v>941</v>
       </c>
       <c r="F32" t="n">
-        <v>1043</v>
+        <v>987</v>
       </c>
       <c r="G32" t="n">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="H32" t="n">
-        <v>1052</v>
+        <v>859</v>
       </c>
       <c r="I32" t="n">
-        <v>927</v>
+        <v>1020</v>
       </c>
       <c r="J32" t="n">
-        <v>1049</v>
+        <v>852</v>
       </c>
       <c r="K32" t="n">
-        <v>1093</v>
+        <v>977</v>
       </c>
       <c r="L32" t="n">
-        <v>998.7</v>
+        <v>970.9</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
+        <v>898</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1135</v>
+      </c>
+      <c r="D33" t="n">
+        <v>940</v>
+      </c>
+      <c r="E33" t="n">
+        <v>973</v>
+      </c>
+      <c r="F33" t="n">
+        <v>975</v>
+      </c>
+      <c r="G33" t="n">
         <v>1109</v>
       </c>
-      <c r="C33" t="n">
-        <v>1015</v>
-      </c>
-      <c r="D33" t="n">
-        <v>986</v>
-      </c>
-      <c r="E33" t="n">
-        <v>913</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1100</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1016</v>
-      </c>
       <c r="H33" t="n">
-        <v>1193</v>
+        <v>993</v>
       </c>
       <c r="I33" t="n">
-        <v>908</v>
+        <v>1257</v>
       </c>
       <c r="J33" t="n">
-        <v>1000</v>
+        <v>1065</v>
       </c>
       <c r="K33" t="n">
-        <v>972</v>
+        <v>1244</v>
       </c>
       <c r="L33" t="n">
-        <v>1021.2</v>
+        <v>1058.9</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1083</v>
+        <v>1066</v>
       </c>
       <c r="C34" t="n">
-        <v>1143</v>
+        <v>984</v>
       </c>
       <c r="D34" t="n">
-        <v>1055</v>
+        <v>1020</v>
       </c>
       <c r="E34" t="n">
-        <v>1002</v>
+        <v>1078</v>
       </c>
       <c r="F34" t="n">
-        <v>1134</v>
+        <v>1013</v>
       </c>
       <c r="G34" t="n">
-        <v>1031</v>
+        <v>1178</v>
       </c>
       <c r="H34" t="n">
-        <v>968</v>
+        <v>1154</v>
       </c>
       <c r="I34" t="n">
-        <v>1049</v>
+        <v>1074</v>
       </c>
       <c r="J34" t="n">
-        <v>943</v>
+        <v>1005</v>
       </c>
       <c r="K34" t="n">
-        <v>1038</v>
+        <v>1096</v>
       </c>
       <c r="L34" t="n">
-        <v>1044.6</v>
+        <v>1066.8</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1296</v>
+        <v>1027</v>
       </c>
       <c r="C35" t="n">
-        <v>1173</v>
+        <v>1041</v>
       </c>
       <c r="D35" t="n">
-        <v>1027</v>
+        <v>1126</v>
       </c>
       <c r="E35" t="n">
-        <v>1308</v>
+        <v>1214</v>
       </c>
       <c r="F35" t="n">
-        <v>1285</v>
+        <v>1220</v>
       </c>
       <c r="G35" t="n">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="H35" t="n">
-        <v>1071</v>
+        <v>942</v>
       </c>
       <c r="I35" t="n">
-        <v>1039</v>
+        <v>1135</v>
       </c>
       <c r="J35" t="n">
-        <v>1029</v>
+        <v>1017</v>
       </c>
       <c r="K35" t="n">
-        <v>1072</v>
+        <v>1120</v>
       </c>
       <c r="L35" t="n">
-        <v>1136.8</v>
+        <v>1090.5</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>973</v>
+        <v>917</v>
       </c>
       <c r="C36" t="n">
-        <v>985</v>
+        <v>1074</v>
       </c>
       <c r="D36" t="n">
-        <v>1002</v>
+        <v>1177</v>
       </c>
       <c r="E36" t="n">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="F36" t="n">
-        <v>966</v>
+        <v>1058</v>
       </c>
       <c r="G36" t="n">
-        <v>1022</v>
+        <v>986</v>
       </c>
       <c r="H36" t="n">
-        <v>998</v>
+        <v>1102</v>
       </c>
       <c r="I36" t="n">
-        <v>1230</v>
+        <v>1143</v>
       </c>
       <c r="J36" t="n">
-        <v>1208</v>
+        <v>949</v>
       </c>
       <c r="K36" t="n">
-        <v>1008</v>
+        <v>1073</v>
       </c>
       <c r="L36" t="n">
-        <v>1041.9</v>
+        <v>1052.3</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>1039</v>
+        <v>1133</v>
       </c>
       <c r="C37" t="n">
-        <v>1275</v>
+        <v>974</v>
       </c>
       <c r="D37" t="n">
+        <v>1178</v>
+      </c>
+      <c r="E37" t="n">
+        <v>988</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1010</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1159</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1043</v>
+      </c>
+      <c r="I37" t="n">
         <v>1098</v>
       </c>
-      <c r="E37" t="n">
-        <v>1019</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1018</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1123</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1073</v>
-      </c>
       <c r="J37" t="n">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="K37" t="n">
-        <v>1149</v>
+        <v>1027</v>
       </c>
       <c r="L37" t="n">
-        <v>1110.7</v>
+        <v>1082.4</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>1161</v>
+        <v>1022</v>
       </c>
       <c r="C38" t="n">
-        <v>1131</v>
+        <v>972</v>
       </c>
       <c r="D38" t="n">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="E38" t="n">
-        <v>1015</v>
+        <v>996</v>
       </c>
       <c r="F38" t="n">
-        <v>893</v>
+        <v>1037</v>
       </c>
       <c r="G38" t="n">
-        <v>1057</v>
+        <v>1103</v>
       </c>
       <c r="H38" t="n">
-        <v>1109</v>
+        <v>1134</v>
       </c>
       <c r="I38" t="n">
-        <v>861</v>
+        <v>1049</v>
       </c>
       <c r="J38" t="n">
-        <v>908</v>
+        <v>953</v>
       </c>
       <c r="K38" t="n">
-        <v>1015</v>
+        <v>894</v>
       </c>
       <c r="L38" t="n">
-        <v>1029.3</v>
+        <v>1030.8</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>1078</v>
+        <v>1208</v>
       </c>
       <c r="C39" t="n">
-        <v>1174</v>
+        <v>1098</v>
       </c>
       <c r="D39" t="n">
-        <v>945</v>
+        <v>882</v>
       </c>
       <c r="E39" t="n">
-        <v>1143</v>
+        <v>1112</v>
       </c>
       <c r="F39" t="n">
+        <v>954</v>
+      </c>
+      <c r="G39" t="n">
         <v>1070</v>
       </c>
-      <c r="G39" t="n">
-        <v>956</v>
-      </c>
       <c r="H39" t="n">
-        <v>925</v>
+        <v>1166</v>
       </c>
       <c r="I39" t="n">
-        <v>950</v>
+        <v>1134</v>
       </c>
       <c r="J39" t="n">
-        <v>1144</v>
+        <v>959</v>
       </c>
       <c r="K39" t="n">
-        <v>1130</v>
+        <v>1185</v>
       </c>
       <c r="L39" t="n">
-        <v>1051.5</v>
+        <v>1076.8</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>1172</v>
+        <v>920</v>
       </c>
       <c r="C40" t="n">
-        <v>1100</v>
+        <v>1023</v>
       </c>
       <c r="D40" t="n">
-        <v>1224</v>
+        <v>1124</v>
       </c>
       <c r="E40" t="n">
-        <v>1135</v>
+        <v>1101</v>
       </c>
       <c r="F40" t="n">
-        <v>1001</v>
+        <v>1307</v>
       </c>
       <c r="G40" t="n">
-        <v>976</v>
+        <v>1242</v>
       </c>
       <c r="H40" t="n">
-        <v>1041</v>
+        <v>1099</v>
       </c>
       <c r="I40" t="n">
-        <v>1078</v>
+        <v>1054</v>
       </c>
       <c r="J40" t="n">
-        <v>963</v>
+        <v>1139</v>
       </c>
       <c r="K40" t="n">
-        <v>1257</v>
+        <v>1035</v>
       </c>
       <c r="L40" t="n">
-        <v>1094.7</v>
+        <v>1104.4</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>981</v>
+        <v>927</v>
       </c>
       <c r="C41" t="n">
-        <v>968</v>
+        <v>1158</v>
       </c>
       <c r="D41" t="n">
-        <v>1104</v>
+        <v>1034</v>
       </c>
       <c r="E41" t="n">
-        <v>1271</v>
+        <v>1023</v>
       </c>
       <c r="F41" t="n">
-        <v>995</v>
+        <v>1029</v>
       </c>
       <c r="G41" t="n">
-        <v>1129</v>
+        <v>1218</v>
       </c>
       <c r="H41" t="n">
-        <v>1097</v>
+        <v>905</v>
       </c>
       <c r="I41" t="n">
-        <v>1079</v>
+        <v>951</v>
       </c>
       <c r="J41" t="n">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="K41" t="n">
-        <v>1024</v>
+        <v>1075</v>
       </c>
       <c r="L41" t="n">
-        <v>1074.8</v>
+        <v>1041.8</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>1050</v>
+        <v>1123</v>
       </c>
       <c r="C42" t="n">
-        <v>1109</v>
+        <v>1018</v>
       </c>
       <c r="D42" t="n">
-        <v>946</v>
+        <v>1040</v>
       </c>
       <c r="E42" t="n">
-        <v>1239</v>
+        <v>1129</v>
       </c>
       <c r="F42" t="n">
-        <v>1037</v>
+        <v>1049</v>
       </c>
       <c r="G42" t="n">
-        <v>1152</v>
+        <v>1000</v>
       </c>
       <c r="H42" t="n">
-        <v>993</v>
+        <v>1015</v>
       </c>
       <c r="I42" t="n">
-        <v>1061</v>
+        <v>1136</v>
       </c>
       <c r="J42" t="n">
-        <v>1064</v>
+        <v>1002</v>
       </c>
       <c r="K42" t="n">
-        <v>1114</v>
+        <v>1016</v>
       </c>
       <c r="L42" t="n">
-        <v>1076.5</v>
+        <v>1052.8</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>1215</v>
+        <v>1042</v>
       </c>
       <c r="C43" t="n">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="D43" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E43" t="n">
         <v>1151</v>
       </c>
-      <c r="E43" t="n">
-        <v>1017</v>
-      </c>
       <c r="F43" t="n">
-        <v>1140</v>
+        <v>1089</v>
       </c>
       <c r="G43" t="n">
-        <v>1042</v>
+        <v>1256</v>
       </c>
       <c r="H43" t="n">
-        <v>1155</v>
+        <v>1000</v>
       </c>
       <c r="I43" t="n">
-        <v>1176</v>
+        <v>1232</v>
       </c>
       <c r="J43" t="n">
-        <v>1079</v>
+        <v>1273</v>
       </c>
       <c r="K43" t="n">
-        <v>1156</v>
+        <v>1043</v>
       </c>
       <c r="L43" t="n">
-        <v>1126.2</v>
+        <v>1141.5</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>987</v>
+        <v>894</v>
       </c>
       <c r="C44" t="n">
-        <v>1181</v>
+        <v>1094</v>
       </c>
       <c r="D44" t="n">
-        <v>1011</v>
+        <v>1205</v>
       </c>
       <c r="E44" t="n">
-        <v>1138</v>
+        <v>1184</v>
       </c>
       <c r="F44" t="n">
-        <v>1093</v>
+        <v>1180</v>
       </c>
       <c r="G44" t="n">
-        <v>1190</v>
+        <v>1025</v>
       </c>
       <c r="H44" t="n">
-        <v>1120</v>
+        <v>1148</v>
       </c>
       <c r="I44" t="n">
-        <v>1143</v>
+        <v>1036</v>
       </c>
       <c r="J44" t="n">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="K44" t="n">
-        <v>1165</v>
+        <v>1064</v>
       </c>
       <c r="L44" t="n">
-        <v>1100.5</v>
+        <v>1080.2</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>987</v>
+        <v>957</v>
       </c>
       <c r="C45" t="n">
-        <v>1142</v>
+        <v>979</v>
       </c>
       <c r="D45" t="n">
-        <v>1049</v>
+        <v>988</v>
       </c>
       <c r="E45" t="n">
-        <v>962</v>
+        <v>993</v>
       </c>
       <c r="F45" t="n">
-        <v>1308</v>
+        <v>1013</v>
       </c>
       <c r="G45" t="n">
-        <v>1088</v>
+        <v>1198</v>
       </c>
       <c r="H45" t="n">
-        <v>1345</v>
+        <v>1169</v>
       </c>
       <c r="I45" t="n">
-        <v>1059</v>
+        <v>1133</v>
       </c>
       <c r="J45" t="n">
-        <v>1058</v>
+        <v>997</v>
       </c>
       <c r="K45" t="n">
-        <v>957</v>
+        <v>945</v>
       </c>
       <c r="L45" t="n">
-        <v>1095.5</v>
+        <v>1037.2</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1172</v>
+        <v>1029</v>
       </c>
       <c r="C46" t="n">
-        <v>1123</v>
+        <v>1023</v>
       </c>
       <c r="D46" t="n">
-        <v>979</v>
+        <v>1167</v>
       </c>
       <c r="E46" t="n">
-        <v>1094</v>
+        <v>1049</v>
       </c>
       <c r="F46" t="n">
-        <v>1106</v>
+        <v>1229</v>
       </c>
       <c r="G46" t="n">
-        <v>1226</v>
+        <v>1247</v>
       </c>
       <c r="H46" t="n">
-        <v>1055</v>
+        <v>1112</v>
       </c>
       <c r="I46" t="n">
-        <v>1231</v>
+        <v>1185</v>
       </c>
       <c r="J46" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="K46" t="n">
-        <v>1089</v>
+        <v>1099</v>
       </c>
       <c r="L46" t="n">
-        <v>1125.4</v>
+        <v>1134.2</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1263</v>
+        <v>1240</v>
       </c>
       <c r="C47" t="n">
-        <v>1128</v>
+        <v>966</v>
       </c>
       <c r="D47" t="n">
-        <v>1138</v>
+        <v>1299</v>
       </c>
       <c r="E47" t="n">
-        <v>1143</v>
+        <v>1026</v>
       </c>
       <c r="F47" t="n">
-        <v>1292</v>
+        <v>1108</v>
       </c>
       <c r="G47" t="n">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H47" t="n">
-        <v>1296</v>
+        <v>1116</v>
       </c>
       <c r="I47" t="n">
-        <v>1005</v>
+        <v>1142</v>
       </c>
       <c r="J47" t="n">
-        <v>996</v>
+        <v>978</v>
       </c>
       <c r="K47" t="n">
-        <v>1131</v>
+        <v>982</v>
       </c>
       <c r="L47" t="n">
-        <v>1145.5</v>
+        <v>1091.9</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>1040</v>
+        <v>1113</v>
       </c>
       <c r="C48" t="n">
-        <v>1098</v>
+        <v>1223</v>
       </c>
       <c r="D48" t="n">
-        <v>1047</v>
+        <v>1111</v>
       </c>
       <c r="E48" t="n">
-        <v>1116</v>
+        <v>1140</v>
       </c>
       <c r="F48" t="n">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="G48" t="n">
-        <v>996</v>
+        <v>1162</v>
       </c>
       <c r="H48" t="n">
-        <v>1139</v>
+        <v>1082</v>
       </c>
       <c r="I48" t="n">
-        <v>1149</v>
+        <v>1176</v>
       </c>
       <c r="J48" t="n">
-        <v>1104</v>
+        <v>935</v>
       </c>
       <c r="K48" t="n">
-        <v>1014</v>
+        <v>1161</v>
       </c>
       <c r="L48" t="n">
-        <v>1088.2</v>
+        <v>1127.9</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1231</v>
+        <v>973</v>
       </c>
       <c r="C49" t="n">
-        <v>1101</v>
+        <v>1133</v>
       </c>
       <c r="D49" t="n">
-        <v>1121</v>
+        <v>1044</v>
       </c>
       <c r="E49" t="n">
-        <v>1104</v>
+        <v>1094</v>
       </c>
       <c r="F49" t="n">
-        <v>1059</v>
+        <v>1068</v>
       </c>
       <c r="G49" t="n">
-        <v>1062</v>
+        <v>1115</v>
       </c>
       <c r="H49" t="n">
-        <v>1165</v>
+        <v>1001</v>
       </c>
       <c r="I49" t="n">
-        <v>929</v>
+        <v>975</v>
       </c>
       <c r="J49" t="n">
-        <v>935</v>
+        <v>991</v>
       </c>
       <c r="K49" t="n">
-        <v>993</v>
+        <v>1023</v>
       </c>
       <c r="L49" t="n">
-        <v>1070</v>
+        <v>1041.7</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="C50" t="n">
-        <v>1138</v>
+        <v>1003</v>
       </c>
       <c r="D50" t="n">
-        <v>1045</v>
+        <v>899</v>
       </c>
       <c r="E50" t="n">
-        <v>1001</v>
+        <v>956</v>
       </c>
       <c r="F50" t="n">
-        <v>893</v>
+        <v>1028</v>
       </c>
       <c r="G50" t="n">
-        <v>1200</v>
+        <v>1129</v>
       </c>
       <c r="H50" t="n">
-        <v>1098</v>
+        <v>999</v>
       </c>
       <c r="I50" t="n">
-        <v>858</v>
+        <v>996</v>
       </c>
       <c r="J50" t="n">
-        <v>1052</v>
+        <v>1092</v>
       </c>
       <c r="K50" t="n">
-        <v>1093</v>
+        <v>986</v>
       </c>
       <c r="L50" t="n">
-        <v>1028</v>
+        <v>999.8</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1080</v>
+        <v>1003</v>
       </c>
       <c r="C51" t="n">
-        <v>988</v>
+        <v>910</v>
       </c>
       <c r="D51" t="n">
-        <v>977</v>
+        <v>1046</v>
       </c>
       <c r="E51" t="n">
-        <v>1075</v>
+        <v>959</v>
       </c>
       <c r="F51" t="n">
-        <v>1122</v>
+        <v>971</v>
       </c>
       <c r="G51" t="n">
-        <v>951</v>
+        <v>1079</v>
       </c>
       <c r="H51" t="n">
-        <v>948</v>
+        <v>1037</v>
       </c>
       <c r="I51" t="n">
-        <v>1006</v>
+        <v>1055</v>
       </c>
       <c r="J51" t="n">
-        <v>987</v>
+        <v>1185</v>
       </c>
       <c r="K51" t="n">
-        <v>1015</v>
+        <v>975</v>
       </c>
       <c r="L51" t="n">
-        <v>1014.9</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1074.1</v>
+        <v>1041.36</v>
       </c>
       <c r="C52" t="n">
-        <v>1106.66</v>
+        <v>1075.64</v>
       </c>
       <c r="D52" t="n">
-        <v>1069.5</v>
+        <v>1078.1</v>
       </c>
       <c r="E52" t="n">
-        <v>1100.06</v>
+        <v>1066.4</v>
       </c>
       <c r="F52" t="n">
-        <v>1096.92</v>
+        <v>1089.88</v>
       </c>
       <c r="G52" t="n">
-        <v>1088.26</v>
+        <v>1098.28</v>
       </c>
       <c r="H52" t="n">
-        <v>1092.96</v>
+        <v>1073.16</v>
       </c>
       <c r="I52" t="n">
-        <v>1071.12</v>
+        <v>1089.42</v>
       </c>
       <c r="J52" t="n">
-        <v>1069.86</v>
+        <v>1048.8</v>
       </c>
       <c r="K52" t="n">
-        <v>1084.68</v>
+        <v>1084.82</v>
       </c>
       <c r="L52" t="n">
-        <v>1085.412</v>
+        <v>1074.586</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>13.07053780555725</v>
+        <v>14.38782906532288</v>
       </c>
       <c r="C2" t="n">
-        <v>14.03253054618835</v>
+        <v>12.4867250919342</v>
       </c>
       <c r="D2" t="n">
-        <v>12.69292211532593</v>
+        <v>14.68231344223022</v>
       </c>
       <c r="E2" t="n">
-        <v>15.18944454193115</v>
+        <v>13.26499485969543</v>
       </c>
       <c r="F2" t="n">
-        <v>13.00315189361572</v>
+        <v>12.60620927810669</v>
       </c>
       <c r="G2" t="n">
-        <v>17.2207179069519</v>
+        <v>12.25219106674194</v>
       </c>
       <c r="H2" t="n">
-        <v>12.34088444709778</v>
+        <v>13.42009282112122</v>
       </c>
       <c r="I2" t="n">
-        <v>15.15007972717285</v>
+        <v>13.64446806907654</v>
       </c>
       <c r="J2" t="n">
-        <v>13.92623472213745</v>
+        <v>13.98313045501709</v>
       </c>
       <c r="K2" t="n">
-        <v>15.33562016487122</v>
+        <v>12.79672169685364</v>
       </c>
       <c r="L2" t="n">
-        <v>14.19621238708496</v>
+        <v>13.35246758460999</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>12.17519354820251</v>
+        <v>11.51849746704102</v>
       </c>
       <c r="C3" t="n">
-        <v>13.8336968421936</v>
+        <v>11.97136878967285</v>
       </c>
       <c r="D3" t="n">
-        <v>12.61684155464172</v>
+        <v>11.84465646743774</v>
       </c>
       <c r="E3" t="n">
-        <v>11.2373321056366</v>
+        <v>10.97991681098938</v>
       </c>
       <c r="F3" t="n">
-        <v>14.44417476654053</v>
+        <v>11.87858033180237</v>
       </c>
       <c r="G3" t="n">
-        <v>11.70764303207397</v>
+        <v>15.01040816307068</v>
       </c>
       <c r="H3" t="n">
-        <v>12.16496872901917</v>
+        <v>16.89655518531799</v>
       </c>
       <c r="I3" t="n">
-        <v>11.80139636993408</v>
+        <v>12.60223054885864</v>
       </c>
       <c r="J3" t="n">
-        <v>12.10962128639221</v>
+        <v>11.67961478233337</v>
       </c>
       <c r="K3" t="n">
-        <v>12.60387063026428</v>
+        <v>16.09560012817383</v>
       </c>
       <c r="L3" t="n">
-        <v>12.46947388648987</v>
+        <v>13.04774286746979</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>17.12209320068359</v>
+        <v>15.69663310050964</v>
       </c>
       <c r="C4" t="n">
-        <v>15.05186462402344</v>
+        <v>12.03265261650085</v>
       </c>
       <c r="D4" t="n">
-        <v>14.72517538070679</v>
+        <v>12.89244985580444</v>
       </c>
       <c r="E4" t="n">
-        <v>13.06897306442261</v>
+        <v>16.97826242446899</v>
       </c>
       <c r="F4" t="n">
-        <v>14.14564633369446</v>
+        <v>12.99139094352722</v>
       </c>
       <c r="G4" t="n">
-        <v>14.1364004611969</v>
+        <v>12.52667284011841</v>
       </c>
       <c r="H4" t="n">
-        <v>15.72506999969482</v>
+        <v>13.08317399024963</v>
       </c>
       <c r="I4" t="n">
-        <v>13.00717067718506</v>
+        <v>12.30913019180298</v>
       </c>
       <c r="J4" t="n">
-        <v>15.45083522796631</v>
+        <v>13.34447574615479</v>
       </c>
       <c r="K4" t="n">
-        <v>17.47829031944275</v>
+        <v>14.58832931518555</v>
       </c>
       <c r="L4" t="n">
-        <v>14.99115192890167</v>
+        <v>13.64431710243225</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>10.86232304573059</v>
+        <v>10.75610876083374</v>
       </c>
       <c r="C5" t="n">
-        <v>11.73357486724854</v>
+        <v>11.21944403648376</v>
       </c>
       <c r="D5" t="n">
-        <v>14.44514322280884</v>
+        <v>11.09621739387512</v>
       </c>
       <c r="E5" t="n">
-        <v>13.05225896835327</v>
+        <v>11.75254774093628</v>
       </c>
       <c r="F5" t="n">
-        <v>12.09616565704346</v>
+        <v>12.05428171157837</v>
       </c>
       <c r="G5" t="n">
-        <v>11.5371778011322</v>
+        <v>11.50117754936218</v>
       </c>
       <c r="H5" t="n">
-        <v>10.9156756401062</v>
+        <v>11.46777844429016</v>
       </c>
       <c r="I5" t="n">
-        <v>11.81275773048401</v>
+        <v>11.64033317565918</v>
       </c>
       <c r="J5" t="n">
-        <v>11.25769758224487</v>
+        <v>11.51419138908386</v>
       </c>
       <c r="K5" t="n">
-        <v>10.36401033401489</v>
+        <v>11.66875600814819</v>
       </c>
       <c r="L5" t="n">
-        <v>11.80767848491669</v>
+        <v>11.46708362102509</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>11.55338358879089</v>
+        <v>12.55648374557495</v>
       </c>
       <c r="C6" t="n">
-        <v>14.71519017219543</v>
+        <v>11.05882096290588</v>
       </c>
       <c r="D6" t="n">
-        <v>12.15188050270081</v>
+        <v>11.71767067909241</v>
       </c>
       <c r="E6" t="n">
-        <v>13.89146614074707</v>
+        <v>12.44833207130432</v>
       </c>
       <c r="F6" t="n">
-        <v>14.1950695514679</v>
+        <v>12.07021570205688</v>
       </c>
       <c r="G6" t="n">
-        <v>11.84419226646423</v>
+        <v>12.00439739227295</v>
       </c>
       <c r="H6" t="n">
-        <v>14.42645287513733</v>
+        <v>13.14100003242493</v>
       </c>
       <c r="I6" t="n">
-        <v>14.95259928703308</v>
+        <v>11.35955619812012</v>
       </c>
       <c r="J6" t="n">
-        <v>13.55122303962708</v>
+        <v>12.50962924957275</v>
       </c>
       <c r="K6" t="n">
-        <v>16.86011624336243</v>
+        <v>12.3381233215332</v>
       </c>
       <c r="L6" t="n">
-        <v>13.81415736675262</v>
+        <v>12.12042293548584</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>11.56139206886292</v>
+        <v>14.34790587425232</v>
       </c>
       <c r="C7" t="n">
-        <v>14.17807936668396</v>
+        <v>13.30557298660278</v>
       </c>
       <c r="D7" t="n">
-        <v>11.99578523635864</v>
+        <v>14.72396397590637</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54683637619019</v>
+        <v>14.12347459793091</v>
       </c>
       <c r="F7" t="n">
-        <v>16.44916439056396</v>
+        <v>11.64831399917603</v>
       </c>
       <c r="G7" t="n">
-        <v>14.68183922767639</v>
+        <v>14.45317506790161</v>
       </c>
       <c r="H7" t="n">
-        <v>14.30824136734009</v>
+        <v>14.52049350738525</v>
       </c>
       <c r="I7" t="n">
-        <v>11.91446852684021</v>
+        <v>14.6576976776123</v>
       </c>
       <c r="J7" t="n">
-        <v>14.48134279251099</v>
+        <v>12.53453826904297</v>
       </c>
       <c r="K7" t="n">
-        <v>12.0970311164856</v>
+        <v>11.57346844673157</v>
       </c>
       <c r="L7" t="n">
-        <v>13.42141804695129</v>
+        <v>13.58886044025421</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>12.07508969306946</v>
+        <v>12.09114265441895</v>
       </c>
       <c r="C8" t="n">
-        <v>11.58336806297302</v>
+        <v>13.15900301933289</v>
       </c>
       <c r="D8" t="n">
-        <v>12.73634696006775</v>
+        <v>13.32454323768616</v>
       </c>
       <c r="E8" t="n">
-        <v>13.08643841743469</v>
+        <v>11.64831733703613</v>
       </c>
       <c r="F8" t="n">
-        <v>14.38105058670044</v>
+        <v>13.30260968208313</v>
       </c>
       <c r="G8" t="n">
-        <v>11.79326748847961</v>
+        <v>11.73457360267639</v>
       </c>
       <c r="H8" t="n">
-        <v>12.10802531242371</v>
+        <v>11.56904673576355</v>
       </c>
       <c r="I8" t="n">
-        <v>12.09052276611328</v>
+        <v>12.18593049049377</v>
       </c>
       <c r="J8" t="n">
-        <v>11.91650128364563</v>
+        <v>12.85225009918213</v>
       </c>
       <c r="K8" t="n">
-        <v>12.12397480010986</v>
+        <v>11.71663188934326</v>
       </c>
       <c r="L8" t="n">
-        <v>12.38945853710175</v>
+        <v>12.35840487480164</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>11.51350569725037</v>
+        <v>11.59446382522583</v>
       </c>
       <c r="C9" t="n">
-        <v>13.80655741691589</v>
+        <v>11.85763835906982</v>
       </c>
       <c r="D9" t="n">
-        <v>13.39410996437073</v>
+        <v>13.08919382095337</v>
       </c>
       <c r="E9" t="n">
-        <v>12.02872037887573</v>
+        <v>11.57896733283997</v>
       </c>
       <c r="F9" t="n">
-        <v>11.58982539176941</v>
+        <v>12.90470051765442</v>
       </c>
       <c r="G9" t="n">
-        <v>12.26239061355591</v>
+        <v>15.64728403091431</v>
       </c>
       <c r="H9" t="n">
-        <v>11.2144193649292</v>
+        <v>14.13571095466614</v>
       </c>
       <c r="I9" t="n">
-        <v>14.21721434593201</v>
+        <v>11.30808115005493</v>
       </c>
       <c r="J9" t="n">
-        <v>14.8571937084198</v>
+        <v>15.36732602119446</v>
       </c>
       <c r="K9" t="n">
-        <v>11.69415020942688</v>
+        <v>12.19388103485107</v>
       </c>
       <c r="L9" t="n">
-        <v>12.65780870914459</v>
+        <v>12.96772470474243</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>11.68418145179749</v>
+        <v>12.5275821685791</v>
       </c>
       <c r="C10" t="n">
-        <v>14.50252509117126</v>
+        <v>14.18384194374084</v>
       </c>
       <c r="D10" t="n">
-        <v>12.53554654121399</v>
+        <v>14.83122730255127</v>
       </c>
       <c r="E10" t="n">
-        <v>14.83693432807922</v>
+        <v>13.5909116268158</v>
       </c>
       <c r="F10" t="n">
-        <v>16.54638767242432</v>
+        <v>12.16901755332947</v>
       </c>
       <c r="G10" t="n">
-        <v>16.54543352127075</v>
+        <v>12.54053664207458</v>
       </c>
       <c r="H10" t="n">
-        <v>12.9358241558075</v>
+        <v>12.87920451164246</v>
       </c>
       <c r="I10" t="n">
-        <v>13.21755957603455</v>
+        <v>12.45234513282776</v>
       </c>
       <c r="J10" t="n">
-        <v>12.24211812019348</v>
+        <v>12.42034482955933</v>
       </c>
       <c r="K10" t="n">
-        <v>11.69921112060547</v>
+        <v>12.31114768981934</v>
       </c>
       <c r="L10" t="n">
-        <v>13.6745721578598</v>
+        <v>12.99061594009399</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>11.88121223449707</v>
+        <v>14.86461281776428</v>
       </c>
       <c r="C11" t="n">
-        <v>12.06635904312134</v>
+        <v>13.32153224945068</v>
       </c>
       <c r="D11" t="n">
-        <v>12.06273031234741</v>
+        <v>12.54253649711609</v>
       </c>
       <c r="E11" t="n">
-        <v>12.80583214759827</v>
+        <v>12.40487718582153</v>
       </c>
       <c r="F11" t="n">
-        <v>12.78340268135071</v>
+        <v>13.42688369750977</v>
       </c>
       <c r="G11" t="n">
-        <v>12.67269158363342</v>
+        <v>12.97098803520203</v>
       </c>
       <c r="H11" t="n">
-        <v>14.66516423225403</v>
+        <v>14.38679790496826</v>
       </c>
       <c r="I11" t="n">
-        <v>13.71006059646606</v>
+        <v>12.2098822593689</v>
       </c>
       <c r="J11" t="n">
-        <v>13.71550583839417</v>
+        <v>13.46920275688171</v>
       </c>
       <c r="K11" t="n">
-        <v>12.3804452419281</v>
+        <v>13.37242364883423</v>
       </c>
       <c r="L11" t="n">
-        <v>12.87434039115906</v>
+        <v>13.29697370529175</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>13.89655756950378</v>
+        <v>16.53236103057861</v>
       </c>
       <c r="C12" t="n">
-        <v>15.35688424110413</v>
+        <v>13.20339274406433</v>
       </c>
       <c r="D12" t="n">
-        <v>18.07194519042969</v>
+        <v>15.24401259422302</v>
       </c>
       <c r="E12" t="n">
-        <v>17.48920226097107</v>
+        <v>12.12261986732483</v>
       </c>
       <c r="F12" t="n">
-        <v>14.70991063117981</v>
+        <v>15.81365942955017</v>
       </c>
       <c r="G12" t="n">
-        <v>16.29305338859558</v>
+        <v>15.65092825889587</v>
       </c>
       <c r="H12" t="n">
-        <v>14.85332489013672</v>
+        <v>16.87105488777161</v>
       </c>
       <c r="I12" t="n">
-        <v>16.10208058357239</v>
+        <v>15.54891681671143</v>
       </c>
       <c r="J12" t="n">
-        <v>13.90034079551697</v>
+        <v>15.52589154243469</v>
       </c>
       <c r="K12" t="n">
-        <v>14.87975382804871</v>
+        <v>15.85267186164856</v>
       </c>
       <c r="L12" t="n">
-        <v>15.55530533790588</v>
+        <v>15.23655090332031</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>16.7269275188446</v>
+        <v>14.98032355308533</v>
       </c>
       <c r="C13" t="n">
-        <v>15.45975399017334</v>
+        <v>13.76743817329407</v>
       </c>
       <c r="D13" t="n">
-        <v>17.21519756317139</v>
+        <v>14.52255439758301</v>
       </c>
       <c r="E13" t="n">
-        <v>16.02926516532898</v>
+        <v>16.04408550262451</v>
       </c>
       <c r="F13" t="n">
-        <v>13.97841215133667</v>
+        <v>16.46950435638428</v>
       </c>
       <c r="G13" t="n">
-        <v>13.6232373714447</v>
+        <v>12.89249658584595</v>
       </c>
       <c r="H13" t="n">
-        <v>16.08900022506714</v>
+        <v>15.78675699234009</v>
       </c>
       <c r="I13" t="n">
-        <v>16.66307783126831</v>
+        <v>18.41914749145508</v>
       </c>
       <c r="J13" t="n">
-        <v>16.46580743789673</v>
+        <v>13.83404636383057</v>
       </c>
       <c r="K13" t="n">
-        <v>14.48804950714111</v>
+        <v>15.74552941322327</v>
       </c>
       <c r="L13" t="n">
-        <v>15.6738728761673</v>
+        <v>15.24618828296661</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>13.14598917961121</v>
+        <v>12.80418515205383</v>
       </c>
       <c r="C14" t="n">
-        <v>12.98638987541199</v>
+        <v>15.54151892662048</v>
       </c>
       <c r="D14" t="n">
-        <v>15.32722330093384</v>
+        <v>13.519850730896</v>
       </c>
       <c r="E14" t="n">
-        <v>16.63755631446838</v>
+        <v>12.86902117729187</v>
       </c>
       <c r="F14" t="n">
-        <v>13.02488970756531</v>
+        <v>16.09013915061951</v>
       </c>
       <c r="G14" t="n">
-        <v>17.97965312004089</v>
+        <v>14.60604023933411</v>
       </c>
       <c r="H14" t="n">
-        <v>15.63732051849365</v>
+        <v>12.48999953269958</v>
       </c>
       <c r="I14" t="n">
-        <v>12.87794494628906</v>
+        <v>14.21250319480896</v>
       </c>
       <c r="J14" t="n">
-        <v>12.97477388381958</v>
+        <v>13.06951928138733</v>
       </c>
       <c r="K14" t="n">
-        <v>14.12172555923462</v>
+        <v>15.75245046615601</v>
       </c>
       <c r="L14" t="n">
-        <v>14.47134664058685</v>
+        <v>14.09552278518677</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>16.07769799232483</v>
+        <v>11.88109159469604</v>
       </c>
       <c r="C15" t="n">
-        <v>12.05460453033447</v>
+        <v>12.50196146965027</v>
       </c>
       <c r="D15" t="n">
-        <v>12.53287291526794</v>
+        <v>11.65465831756592</v>
       </c>
       <c r="E15" t="n">
-        <v>13.81701111793518</v>
+        <v>11.95340156555176</v>
       </c>
       <c r="F15" t="n">
-        <v>12.71246743202209</v>
+        <v>13.47245121002197</v>
       </c>
       <c r="G15" t="n">
-        <v>12.77124214172363</v>
+        <v>15.2972366809845</v>
       </c>
       <c r="H15" t="n">
-        <v>14.68633961677551</v>
+        <v>12.73533725738525</v>
       </c>
       <c r="I15" t="n">
-        <v>12.32261681556702</v>
+        <v>12.69745087623596</v>
       </c>
       <c r="J15" t="n">
-        <v>12.13452196121216</v>
+        <v>11.7194836139679</v>
       </c>
       <c r="K15" t="n">
-        <v>15.19030618667603</v>
+        <v>12.27605438232422</v>
       </c>
       <c r="L15" t="n">
-        <v>13.42996807098389</v>
+        <v>12.61891269683838</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>11.8981614112854</v>
+        <v>12.9199001789093</v>
       </c>
       <c r="C16" t="n">
-        <v>12.65573382377625</v>
+        <v>12.66206216812134</v>
       </c>
       <c r="D16" t="n">
-        <v>14.8541522026062</v>
+        <v>12.40320873260498</v>
       </c>
       <c r="E16" t="n">
-        <v>12.9361424446106</v>
+        <v>15.70645022392273</v>
       </c>
       <c r="F16" t="n">
-        <v>16.85402894020081</v>
+        <v>12.38792133331299</v>
       </c>
       <c r="G16" t="n">
-        <v>13.61339592933655</v>
+        <v>11.61140012741089</v>
       </c>
       <c r="H16" t="n">
-        <v>13.49413228034973</v>
+        <v>12.99687123298645</v>
       </c>
       <c r="I16" t="n">
-        <v>12.43029642105103</v>
+        <v>18.31325244903564</v>
       </c>
       <c r="J16" t="n">
-        <v>15.558842420578</v>
+        <v>12.26724100112915</v>
       </c>
       <c r="K16" t="n">
-        <v>12.60882472991943</v>
+        <v>16.19221639633179</v>
       </c>
       <c r="L16" t="n">
-        <v>13.6903710603714</v>
+        <v>13.74605238437653</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>12.8652491569519</v>
+        <v>11.71612310409546</v>
       </c>
       <c r="C17" t="n">
-        <v>11.85429930686951</v>
+        <v>14.82920956611633</v>
       </c>
       <c r="D17" t="n">
-        <v>15.74634790420532</v>
+        <v>12.57200002670288</v>
       </c>
       <c r="E17" t="n">
-        <v>12.40486073493958</v>
+        <v>12.23181056976318</v>
       </c>
       <c r="F17" t="n">
-        <v>11.84634232521057</v>
+        <v>11.10320925712585</v>
       </c>
       <c r="G17" t="n">
-        <v>11.45080757141113</v>
+        <v>11.48072242736816</v>
       </c>
       <c r="H17" t="n">
-        <v>12.14753198623657</v>
+        <v>12.25281834602356</v>
       </c>
       <c r="I17" t="n">
-        <v>11.87572479248047</v>
+        <v>11.68080353736877</v>
       </c>
       <c r="J17" t="n">
-        <v>14.11348581314087</v>
+        <v>11.79391360282898</v>
       </c>
       <c r="K17" t="n">
-        <v>11.8448224067688</v>
+        <v>17.15175628662109</v>
       </c>
       <c r="L17" t="n">
-        <v>12.61494719982147</v>
+        <v>12.68123667240143</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>15.84057545661926</v>
+        <v>14.84236407279968</v>
       </c>
       <c r="C18" t="n">
-        <v>16.561274766922</v>
+        <v>15.27968001365662</v>
       </c>
       <c r="D18" t="n">
-        <v>12.43535041809082</v>
+        <v>12.24849724769592</v>
       </c>
       <c r="E18" t="n">
-        <v>14.32900905609131</v>
+        <v>13.06871867179871</v>
       </c>
       <c r="F18" t="n">
-        <v>14.78978109359741</v>
+        <v>14.24177098274231</v>
       </c>
       <c r="G18" t="n">
-        <v>14.75041317939758</v>
+        <v>16.64361596107483</v>
       </c>
       <c r="H18" t="n">
-        <v>13.53799390792847</v>
+        <v>11.22438216209412</v>
       </c>
       <c r="I18" t="n">
-        <v>14.47507834434509</v>
+        <v>11.89320635795593</v>
       </c>
       <c r="J18" t="n">
-        <v>13.56112504005432</v>
+        <v>12.67465853691101</v>
       </c>
       <c r="K18" t="n">
-        <v>12.15037703514099</v>
+        <v>12.55056262016296</v>
       </c>
       <c r="L18" t="n">
-        <v>14.24309782981873</v>
+        <v>13.46674566268921</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>14.46032643318176</v>
+        <v>12.93956303596497</v>
       </c>
       <c r="C19" t="n">
-        <v>15.37846970558167</v>
+        <v>14.48503589630127</v>
       </c>
       <c r="D19" t="n">
-        <v>12.56829857826233</v>
+        <v>11.99144220352173</v>
       </c>
       <c r="E19" t="n">
-        <v>13.50033378601074</v>
+        <v>11.94407486915588</v>
       </c>
       <c r="F19" t="n">
-        <v>13.89382743835449</v>
+        <v>12.91856408119202</v>
       </c>
       <c r="G19" t="n">
-        <v>15.36850643157959</v>
+        <v>12.02136850357056</v>
       </c>
       <c r="H19" t="n">
-        <v>12.76970505714417</v>
+        <v>11.93410587310791</v>
       </c>
       <c r="I19" t="n">
-        <v>11.62534093856812</v>
+        <v>15.57884883880615</v>
       </c>
       <c r="J19" t="n">
-        <v>15.31645250320435</v>
+        <v>14.39728116989136</v>
       </c>
       <c r="K19" t="n">
-        <v>11.98494482040405</v>
+        <v>12.85023307800293</v>
       </c>
       <c r="L19" t="n">
-        <v>13.68662056922913</v>
+        <v>13.10605175495148</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>12.65625262260437</v>
+        <v>13.39035606384277</v>
       </c>
       <c r="C20" t="n">
-        <v>13.85773539543152</v>
+        <v>11.68979024887085</v>
       </c>
       <c r="D20" t="n">
-        <v>13.48167276382446</v>
+        <v>15.48848485946655</v>
       </c>
       <c r="E20" t="n">
-        <v>14.03020548820496</v>
+        <v>11.36903190612793</v>
       </c>
       <c r="F20" t="n">
-        <v>13.82969260215759</v>
+        <v>13.62627911567688</v>
       </c>
       <c r="G20" t="n">
-        <v>14.59678959846497</v>
+        <v>13.72064661979675</v>
       </c>
       <c r="H20" t="n">
-        <v>13.6003201007843</v>
+        <v>15.10251569747925</v>
       </c>
       <c r="I20" t="n">
-        <v>15.39521455764771</v>
+        <v>13.66769862174988</v>
       </c>
       <c r="J20" t="n">
-        <v>11.59844160079956</v>
+        <v>11.96099638938904</v>
       </c>
       <c r="K20" t="n">
-        <v>13.18982863426208</v>
+        <v>15.5488646030426</v>
       </c>
       <c r="L20" t="n">
-        <v>13.62361533641815</v>
+        <v>13.55646641254425</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>11.32865190505981</v>
+        <v>12.59991192817688</v>
       </c>
       <c r="C21" t="n">
-        <v>14.23370575904846</v>
+        <v>12.87520313262939</v>
       </c>
       <c r="D21" t="n">
-        <v>12.4133186340332</v>
+        <v>12.20987558364868</v>
       </c>
       <c r="E21" t="n">
-        <v>12.85520768165588</v>
+        <v>13.0427713394165</v>
       </c>
       <c r="F21" t="n">
-        <v>13.30758810043335</v>
+        <v>12.81539344787598</v>
       </c>
       <c r="G21" t="n">
-        <v>11.88266348838806</v>
+        <v>12.30914282798767</v>
       </c>
       <c r="H21" t="n">
-        <v>12.54452705383301</v>
+        <v>12.43531107902527</v>
       </c>
       <c r="I21" t="n">
-        <v>15.12296557426453</v>
+        <v>12.5644953250885</v>
       </c>
       <c r="J21" t="n">
-        <v>12.82333087921143</v>
+        <v>11.52709269523621</v>
       </c>
       <c r="K21" t="n">
-        <v>15.67807197570801</v>
+        <v>11.65783309936523</v>
       </c>
       <c r="L21" t="n">
-        <v>13.21900310516357</v>
+        <v>12.40370304584503</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>15.25210881233215</v>
+        <v>12.51264882087708</v>
       </c>
       <c r="C22" t="n">
-        <v>13.20481610298157</v>
+        <v>14.19928431510925</v>
       </c>
       <c r="D22" t="n">
-        <v>16.33084464073181</v>
+        <v>11.97548055648804</v>
       </c>
       <c r="E22" t="n">
-        <v>12.69215536117554</v>
+        <v>12.33707571029663</v>
       </c>
       <c r="F22" t="n">
-        <v>12.48364067077637</v>
+        <v>11.40508532524109</v>
       </c>
       <c r="G22" t="n">
-        <v>13.12253737449646</v>
+        <v>12.73240280151367</v>
       </c>
       <c r="H22" t="n">
-        <v>12.38344478607178</v>
+        <v>12.82839179039001</v>
       </c>
       <c r="I22" t="n">
-        <v>11.47276401519775</v>
+        <v>17.68195462226868</v>
       </c>
       <c r="J22" t="n">
-        <v>12.18296909332275</v>
+        <v>13.07597208023071</v>
       </c>
       <c r="K22" t="n">
-        <v>11.87172365188599</v>
+        <v>13.31880140304565</v>
       </c>
       <c r="L22" t="n">
-        <v>13.09970045089722</v>
+        <v>13.20670974254608</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>10.5416259765625</v>
+        <v>11.24972319602966</v>
       </c>
       <c r="C23" t="n">
-        <v>13.96589207649231</v>
+        <v>12.69995594024658</v>
       </c>
       <c r="D23" t="n">
-        <v>10.67731261253357</v>
+        <v>11.12502217292786</v>
       </c>
       <c r="E23" t="n">
-        <v>12.79212856292725</v>
+        <v>13.01366686820984</v>
       </c>
       <c r="F23" t="n">
-        <v>10.76896142959595</v>
+        <v>12.27455973625183</v>
       </c>
       <c r="G23" t="n">
-        <v>11.20881462097168</v>
+        <v>13.94619512557983</v>
       </c>
       <c r="H23" t="n">
-        <v>11.15861034393311</v>
+        <v>11.58585500717163</v>
       </c>
       <c r="I23" t="n">
-        <v>11.44486260414124</v>
+        <v>12.59371638298035</v>
       </c>
       <c r="J23" t="n">
-        <v>13.51904273033142</v>
+        <v>11.99184203147888</v>
       </c>
       <c r="K23" t="n">
-        <v>12.07819700241089</v>
+        <v>15.52390432357788</v>
       </c>
       <c r="L23" t="n">
-        <v>11.81554479598999</v>
+        <v>12.60044407844543</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>12.64772510528564</v>
+        <v>13.14601421356201</v>
       </c>
       <c r="C24" t="n">
-        <v>13.34047365188599</v>
+        <v>12.62082242965698</v>
       </c>
       <c r="D24" t="n">
-        <v>12.15251183509827</v>
+        <v>18.09739017486572</v>
       </c>
       <c r="E24" t="n">
-        <v>13.09814882278442</v>
+        <v>13.56272029876709</v>
       </c>
       <c r="F24" t="n">
-        <v>12.30113244056702</v>
+        <v>13.36369729042053</v>
       </c>
       <c r="G24" t="n">
-        <v>12.48817706108093</v>
+        <v>12.34885740280151</v>
       </c>
       <c r="H24" t="n">
-        <v>12.17695546150208</v>
+        <v>15.46276807785034</v>
       </c>
       <c r="I24" t="n">
-        <v>12.69561243057251</v>
+        <v>15.22737383842468</v>
       </c>
       <c r="J24" t="n">
-        <v>12.92760276794434</v>
+        <v>13.21364521980286</v>
       </c>
       <c r="K24" t="n">
-        <v>12.90961885452271</v>
+        <v>12.38000774383545</v>
       </c>
       <c r="L24" t="n">
-        <v>12.67379584312439</v>
+        <v>13.94232966899872</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>15.76081490516663</v>
+        <v>13.21451783180237</v>
       </c>
       <c r="C25" t="n">
-        <v>16.7647271156311</v>
+        <v>19.06943154335022</v>
       </c>
       <c r="D25" t="n">
-        <v>14.78181409835815</v>
+        <v>16.07652378082275</v>
       </c>
       <c r="E25" t="n">
-        <v>18.28685998916626</v>
+        <v>14.87211465835571</v>
       </c>
       <c r="F25" t="n">
-        <v>13.8122832775116</v>
+        <v>17.66608881950378</v>
       </c>
       <c r="G25" t="n">
-        <v>16.69294142723083</v>
+        <v>14.37663078308105</v>
       </c>
       <c r="H25" t="n">
-        <v>14.69801902770996</v>
+        <v>14.28483724594116</v>
       </c>
       <c r="I25" t="n">
-        <v>14.26361680030823</v>
+        <v>13.75419068336487</v>
       </c>
       <c r="J25" t="n">
-        <v>14.16174411773682</v>
+        <v>14.10330939292908</v>
       </c>
       <c r="K25" t="n">
-        <v>14.57807970046997</v>
+        <v>16.95937085151672</v>
       </c>
       <c r="L25" t="n">
-        <v>15.38009004592896</v>
+        <v>15.43770155906677</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>11.8342010974884</v>
+        <v>10.87872433662415</v>
       </c>
       <c r="C26" t="n">
-        <v>10.7235803604126</v>
+        <v>12.80868458747864</v>
       </c>
       <c r="D26" t="n">
-        <v>10.88869094848633</v>
+        <v>14.62293934822083</v>
       </c>
       <c r="E26" t="n">
-        <v>11.67213010787964</v>
+        <v>14.4315025806427</v>
       </c>
       <c r="F26" t="n">
-        <v>10.53606724739075</v>
+        <v>11.74395155906677</v>
       </c>
       <c r="G26" t="n">
-        <v>10.83582830429077</v>
+        <v>10.42290472984314</v>
       </c>
       <c r="H26" t="n">
-        <v>12.07106113433838</v>
+        <v>10.27581119537354</v>
       </c>
       <c r="I26" t="n">
-        <v>10.5839250087738</v>
+        <v>11.28168773651123</v>
       </c>
       <c r="J26" t="n">
-        <v>10.38995718955994</v>
+        <v>12.35943412780762</v>
       </c>
       <c r="K26" t="n">
-        <v>12.18078970909119</v>
+        <v>10.24679923057556</v>
       </c>
       <c r="L26" t="n">
-        <v>11.17162311077118</v>
+        <v>11.90724394321442</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>16.70208191871643</v>
+        <v>12.49657464027405</v>
       </c>
       <c r="C27" t="n">
-        <v>12.67102289199829</v>
+        <v>15.5390899181366</v>
       </c>
       <c r="D27" t="n">
-        <v>13.50684690475464</v>
+        <v>17.02843880653381</v>
       </c>
       <c r="E27" t="n">
-        <v>16.58972549438477</v>
+        <v>15.35786581039429</v>
       </c>
       <c r="F27" t="n">
-        <v>15.39824533462524</v>
+        <v>12.06533169746399</v>
       </c>
       <c r="G27" t="n">
-        <v>13.55444407463074</v>
+        <v>12.34807229042053</v>
       </c>
       <c r="H27" t="n">
-        <v>12.22682642936707</v>
+        <v>13.33850121498108</v>
       </c>
       <c r="I27" t="n">
-        <v>14.73970246315002</v>
+        <v>14.11748957633972</v>
       </c>
       <c r="J27" t="n">
-        <v>17.55581164360046</v>
+        <v>15.90905976295471</v>
       </c>
       <c r="K27" t="n">
-        <v>15.42404723167419</v>
+        <v>14.78679037094116</v>
       </c>
       <c r="L27" t="n">
-        <v>14.83687543869019</v>
+        <v>14.29872140884399</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>14.21872854232788</v>
+        <v>13.20782732963562</v>
       </c>
       <c r="C28" t="n">
-        <v>12.48066735267639</v>
+        <v>12.01238703727722</v>
       </c>
       <c r="D28" t="n">
-        <v>15.30401349067688</v>
+        <v>14.16688323020935</v>
       </c>
       <c r="E28" t="n">
-        <v>11.74107336997986</v>
+        <v>13.87659668922424</v>
       </c>
       <c r="F28" t="n">
-        <v>14.01876187324524</v>
+        <v>14.91347312927246</v>
       </c>
       <c r="G28" t="n">
-        <v>12.42030501365662</v>
+        <v>11.28023505210876</v>
       </c>
       <c r="H28" t="n">
-        <v>13.83569812774658</v>
+        <v>11.65781927108765</v>
       </c>
       <c r="I28" t="n">
-        <v>11.29572439193726</v>
+        <v>12.11012959480286</v>
       </c>
       <c r="J28" t="n">
-        <v>12.93151473999023</v>
+        <v>11.95314741134644</v>
       </c>
       <c r="K28" t="n">
-        <v>14.26409077644348</v>
+        <v>11.34697151184082</v>
       </c>
       <c r="L28" t="n">
-        <v>13.25105776786804</v>
+        <v>12.65254702568054</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>12.05161190032959</v>
+        <v>11.60576415061951</v>
       </c>
       <c r="C29" t="n">
-        <v>13.23549246788025</v>
+        <v>14.16163396835327</v>
       </c>
       <c r="D29" t="n">
-        <v>12.42569088935852</v>
+        <v>10.54106998443604</v>
       </c>
       <c r="E29" t="n">
-        <v>11.56649899482727</v>
+        <v>10.96149063110352</v>
       </c>
       <c r="F29" t="n">
-        <v>14.04017210006714</v>
+        <v>13.35973691940308</v>
       </c>
       <c r="G29" t="n">
-        <v>14.56685543060303</v>
+        <v>14.81243848800659</v>
       </c>
       <c r="H29" t="n">
-        <v>13.84076738357544</v>
+        <v>11.95940399169922</v>
       </c>
       <c r="I29" t="n">
-        <v>10.97249889373779</v>
+        <v>10.89214277267456</v>
       </c>
       <c r="J29" t="n">
-        <v>10.97700023651123</v>
+        <v>11.81025385856628</v>
       </c>
       <c r="K29" t="n">
-        <v>11.9579803943634</v>
+        <v>10.74950933456421</v>
       </c>
       <c r="L29" t="n">
-        <v>12.56345686912537</v>
+        <v>12.08534440994263</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>14.30903577804565</v>
+        <v>15.20122933387756</v>
       </c>
       <c r="C30" t="n">
-        <v>13.12900233268738</v>
+        <v>17.16277194023132</v>
       </c>
       <c r="D30" t="n">
-        <v>14.28954744338989</v>
+        <v>14.19884061813354</v>
       </c>
       <c r="E30" t="n">
-        <v>13.84174108505249</v>
+        <v>11.30716824531555</v>
       </c>
       <c r="F30" t="n">
-        <v>12.76446652412415</v>
+        <v>12.26125144958496</v>
       </c>
       <c r="G30" t="n">
-        <v>14.69452571868896</v>
+        <v>16.49504947662354</v>
       </c>
       <c r="H30" t="n">
-        <v>14.81020569801331</v>
+        <v>14.13947510719299</v>
       </c>
       <c r="I30" t="n">
-        <v>13.80282115936279</v>
+        <v>15.78312301635742</v>
       </c>
       <c r="J30" t="n">
-        <v>11.53308129310608</v>
+        <v>16.56327652931213</v>
       </c>
       <c r="K30" t="n">
-        <v>13.57387351989746</v>
+        <v>15.08107495307922</v>
       </c>
       <c r="L30" t="n">
-        <v>13.67483005523682</v>
+        <v>14.81932606697083</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>12.56099152565002</v>
+        <v>20.06509470939636</v>
       </c>
       <c r="C31" t="n">
-        <v>12.89813613891602</v>
+        <v>12.3590075969696</v>
       </c>
       <c r="D31" t="n">
-        <v>12.46876764297485</v>
+        <v>15.63517117500305</v>
       </c>
       <c r="E31" t="n">
-        <v>12.53853678703308</v>
+        <v>13.97316288948059</v>
       </c>
       <c r="F31" t="n">
-        <v>14.63971519470215</v>
+        <v>17.95357060432434</v>
       </c>
       <c r="G31" t="n">
-        <v>11.33956527709961</v>
+        <v>14.89308166503906</v>
       </c>
       <c r="H31" t="n">
-        <v>15.74633550643921</v>
+        <v>16.04015445709229</v>
       </c>
       <c r="I31" t="n">
-        <v>18.17416143417358</v>
+        <v>13.08322095870972</v>
       </c>
       <c r="J31" t="n">
-        <v>15.28850793838501</v>
+        <v>12.70710134506226</v>
       </c>
       <c r="K31" t="n">
-        <v>14.6775643825531</v>
+        <v>15.74846482276917</v>
       </c>
       <c r="L31" t="n">
-        <v>14.03322818279266</v>
+        <v>15.24580302238464</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>10.65480613708496</v>
+        <v>12.26074004173279</v>
       </c>
       <c r="C32" t="n">
-        <v>12.58041024208069</v>
+        <v>13.28066778182983</v>
       </c>
       <c r="D32" t="n">
-        <v>11.44833159446716</v>
+        <v>15.97177624702454</v>
       </c>
       <c r="E32" t="n">
-        <v>14.88442540168762</v>
+        <v>11.31274342536926</v>
       </c>
       <c r="F32" t="n">
-        <v>12.24018168449402</v>
+        <v>12.00180888175964</v>
       </c>
       <c r="G32" t="n">
-        <v>12.41671895980835</v>
+        <v>13.45598530769348</v>
       </c>
       <c r="H32" t="n">
-        <v>15.65522289276123</v>
+        <v>11.4466450214386</v>
       </c>
       <c r="I32" t="n">
-        <v>13.14626002311707</v>
+        <v>12.93850159645081</v>
       </c>
       <c r="J32" t="n">
-        <v>13.23805379867554</v>
+        <v>11.93161058425903</v>
       </c>
       <c r="K32" t="n">
-        <v>11.92742109298706</v>
+        <v>11.78247451782227</v>
       </c>
       <c r="L32" t="n">
-        <v>12.81918318271637</v>
+        <v>12.63829534053803</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>12.88644433021545</v>
+        <v>12.70016813278198</v>
       </c>
       <c r="C33" t="n">
-        <v>11.93078899383545</v>
+        <v>15.47059369087219</v>
       </c>
       <c r="D33" t="n">
-        <v>12.37643527984619</v>
+        <v>11.77900409698486</v>
       </c>
       <c r="E33" t="n">
-        <v>12.07622575759888</v>
+        <v>11.54708433151245</v>
       </c>
       <c r="F33" t="n">
-        <v>14.35495281219482</v>
+        <v>11.53913164138794</v>
       </c>
       <c r="G33" t="n">
-        <v>12.27021336555481</v>
+        <v>14.80832600593567</v>
       </c>
       <c r="H33" t="n">
-        <v>14.60777807235718</v>
+        <v>12.57145571708679</v>
       </c>
       <c r="I33" t="n">
-        <v>12.00889420509338</v>
+        <v>15.41570663452148</v>
       </c>
       <c r="J33" t="n">
-        <v>12.66622567176819</v>
+        <v>12.64080452919006</v>
       </c>
       <c r="K33" t="n">
-        <v>12.49517202377319</v>
+        <v>15.38982105255127</v>
       </c>
       <c r="L33" t="n">
-        <v>12.76731305122376</v>
+        <v>13.38620958328247</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>11.82784080505371</v>
+        <v>12.71607661247253</v>
       </c>
       <c r="C34" t="n">
-        <v>13.0238151550293</v>
+        <v>11.23342704772949</v>
       </c>
       <c r="D34" t="n">
-        <v>11.58896422386169</v>
+        <v>12.83833432197571</v>
       </c>
       <c r="E34" t="n">
-        <v>12.35948967933655</v>
+        <v>11.86430072784424</v>
       </c>
       <c r="F34" t="n">
-        <v>13.03005576133728</v>
+        <v>11.39350008964539</v>
       </c>
       <c r="G34" t="n">
-        <v>11.81984949111938</v>
+        <v>13.78384900093079</v>
       </c>
       <c r="H34" t="n">
-        <v>11.21041655540466</v>
+        <v>11.21641540527344</v>
       </c>
       <c r="I34" t="n">
-        <v>11.93711233139038</v>
+        <v>11.37249326705933</v>
       </c>
       <c r="J34" t="n">
-        <v>10.3735363483429</v>
+        <v>11.36801242828369</v>
       </c>
       <c r="K34" t="n">
-        <v>11.36150240898132</v>
+        <v>13.61577725410461</v>
       </c>
       <c r="L34" t="n">
-        <v>11.85325827598572</v>
+        <v>12.14021861553192</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>17.76668334007263</v>
+        <v>11.79241180419922</v>
       </c>
       <c r="C35" t="n">
-        <v>16.23662209510803</v>
+        <v>13.09911727905273</v>
       </c>
       <c r="D35" t="n">
-        <v>12.66471982002258</v>
+        <v>14.53614258766174</v>
       </c>
       <c r="E35" t="n">
-        <v>15.39478158950806</v>
+        <v>16.50950360298157</v>
       </c>
       <c r="F35" t="n">
-        <v>17.62750554084778</v>
+        <v>16.26452803611755</v>
       </c>
       <c r="G35" t="n">
-        <v>12.24726438522339</v>
+        <v>13.13799905776978</v>
       </c>
       <c r="H35" t="n">
-        <v>13.34146451950073</v>
+        <v>12.26077771186829</v>
       </c>
       <c r="I35" t="n">
-        <v>12.56644248962402</v>
+        <v>11.89819359779358</v>
       </c>
       <c r="J35" t="n">
-        <v>12.35399317741394</v>
+        <v>11.80472755432129</v>
       </c>
       <c r="K35" t="n">
-        <v>11.70763921737671</v>
+        <v>14.22973585128784</v>
       </c>
       <c r="L35" t="n">
-        <v>14.19071161746979</v>
+        <v>13.55331370830536</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>11.92121028900146</v>
+        <v>11.8792200088501</v>
       </c>
       <c r="C36" t="n">
-        <v>11.85977292060852</v>
+        <v>13.64793348312378</v>
       </c>
       <c r="D36" t="n">
-        <v>12.01636838912964</v>
+        <v>13.24555063247681</v>
       </c>
       <c r="E36" t="n">
-        <v>11.91116142272949</v>
+        <v>12.80566048622131</v>
       </c>
       <c r="F36" t="n">
-        <v>12.62780594825745</v>
+        <v>15.29910469055176</v>
       </c>
       <c r="G36" t="n">
-        <v>12.90359234809875</v>
+        <v>12.59740805625916</v>
       </c>
       <c r="H36" t="n">
-        <v>12.50261521339417</v>
+        <v>13.9339816570282</v>
       </c>
       <c r="I36" t="n">
-        <v>17.33830070495605</v>
+        <v>12.53356695175171</v>
       </c>
       <c r="J36" t="n">
-        <v>15.23214530944824</v>
+        <v>11.51717090606689</v>
       </c>
       <c r="K36" t="n">
-        <v>12.22431421279907</v>
+        <v>12.41042041778564</v>
       </c>
       <c r="L36" t="n">
-        <v>13.05372867584228</v>
+        <v>12.98700172901153</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>11.39719319343567</v>
+        <v>13.25775980949402</v>
       </c>
       <c r="C37" t="n">
-        <v>16.78431940078735</v>
+        <v>11.79246497154236</v>
       </c>
       <c r="D37" t="n">
-        <v>12.038654088974</v>
+        <v>14.66644716262817</v>
       </c>
       <c r="E37" t="n">
-        <v>12.97796225547791</v>
+        <v>14.15241456031799</v>
       </c>
       <c r="F37" t="n">
-        <v>12.84027361869812</v>
+        <v>12.21775817871094</v>
       </c>
       <c r="G37" t="n">
-        <v>11.68071961402893</v>
+        <v>13.46869373321533</v>
       </c>
       <c r="H37" t="n">
-        <v>15.05957698822021</v>
+        <v>12.02533292770386</v>
       </c>
       <c r="I37" t="n">
-        <v>11.81286835670471</v>
+        <v>14.06413388252258</v>
       </c>
       <c r="J37" t="n">
-        <v>14.64662957191467</v>
+        <v>13.41678977012634</v>
       </c>
       <c r="K37" t="n">
-        <v>13.85367822647095</v>
+        <v>12.10066294670105</v>
       </c>
       <c r="L37" t="n">
-        <v>13.30918753147125</v>
+        <v>13.11624579429627</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>14.83020067214966</v>
+        <v>12.83827662467957</v>
       </c>
       <c r="C38" t="n">
-        <v>14.78077578544617</v>
+        <v>12.5495343208313</v>
       </c>
       <c r="D38" t="n">
-        <v>15.01474285125732</v>
+        <v>17.84451723098755</v>
       </c>
       <c r="E38" t="n">
-        <v>11.88870978355408</v>
+        <v>12.16499781608582</v>
       </c>
       <c r="F38" t="n">
-        <v>11.52013540267944</v>
+        <v>12.17643618583679</v>
       </c>
       <c r="G38" t="n">
-        <v>12.15398478507996</v>
+        <v>12.54852271080017</v>
       </c>
       <c r="H38" t="n">
-        <v>11.9155969619751</v>
+        <v>14.91356587409973</v>
       </c>
       <c r="I38" t="n">
-        <v>12.08874773979187</v>
+        <v>13.41015863418579</v>
       </c>
       <c r="J38" t="n">
-        <v>12.26871800422668</v>
+        <v>12.28551363945007</v>
       </c>
       <c r="K38" t="n">
-        <v>12.26728534698486</v>
+        <v>13.13131022453308</v>
       </c>
       <c r="L38" t="n">
-        <v>12.87288973331451</v>
+        <v>13.38628332614899</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>11.36055684089661</v>
+        <v>15.94302225112915</v>
       </c>
       <c r="C39" t="n">
-        <v>13.8298602104187</v>
+        <v>11.07720351219177</v>
       </c>
       <c r="D39" t="n">
-        <v>11.49958205223083</v>
+        <v>10.21043920516968</v>
       </c>
       <c r="E39" t="n">
-        <v>13.63051629066467</v>
+        <v>12.99314117431641</v>
       </c>
       <c r="F39" t="n">
-        <v>11.9344322681427</v>
+        <v>11.03231549263</v>
       </c>
       <c r="G39" t="n">
-        <v>10.44483470916748</v>
+        <v>12.79172468185425</v>
       </c>
       <c r="H39" t="n">
-        <v>10.98043894767761</v>
+        <v>13.85091352462769</v>
       </c>
       <c r="I39" t="n">
-        <v>9.673871040344238</v>
+        <v>11.21881985664368</v>
       </c>
       <c r="J39" t="n">
-        <v>12.78674340248108</v>
+        <v>10.74252367019653</v>
       </c>
       <c r="K39" t="n">
-        <v>13.67936682701111</v>
+        <v>13.26647734642029</v>
       </c>
       <c r="L39" t="n">
-        <v>11.9820202589035</v>
+        <v>12.31265807151794</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>15.89466857910156</v>
+        <v>12.31497168540955</v>
       </c>
       <c r="C40" t="n">
-        <v>14.49874782562256</v>
+        <v>12.85107016563416</v>
       </c>
       <c r="D40" t="n">
-        <v>15.80985355377197</v>
+        <v>15.52611017227173</v>
       </c>
       <c r="E40" t="n">
-        <v>12.37426900863647</v>
+        <v>14.62893319129944</v>
       </c>
       <c r="F40" t="n">
-        <v>12.10895371437073</v>
+        <v>16.34861874580383</v>
       </c>
       <c r="G40" t="n">
-        <v>12.68196582794189</v>
+        <v>13.73746228218079</v>
       </c>
       <c r="H40" t="n">
-        <v>12.21322417259216</v>
+        <v>15.62019515037537</v>
       </c>
       <c r="I40" t="n">
-        <v>13.10938453674316</v>
+        <v>14.55204606056213</v>
       </c>
       <c r="J40" t="n">
-        <v>12.43463921546936</v>
+        <v>15.42722511291504</v>
       </c>
       <c r="K40" t="n">
-        <v>14.51679062843323</v>
+        <v>13.04422426223755</v>
       </c>
       <c r="L40" t="n">
-        <v>13.56424970626831</v>
+        <v>14.40508568286896</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>11.30607748031616</v>
+        <v>11.50417470932007</v>
       </c>
       <c r="C41" t="n">
-        <v>10.98791027069092</v>
+        <v>13.67316889762878</v>
       </c>
       <c r="D41" t="n">
-        <v>13.34324073791504</v>
+        <v>11.95703077316284</v>
       </c>
       <c r="E41" t="n">
-        <v>13.87786984443665</v>
+        <v>12.50862836837769</v>
       </c>
       <c r="F41" t="n">
-        <v>11.38896632194519</v>
+        <v>12.02236151695251</v>
       </c>
       <c r="G41" t="n">
-        <v>14.57169008255005</v>
+        <v>12.59987735748291</v>
       </c>
       <c r="H41" t="n">
-        <v>14.23071837425232</v>
+        <v>10.47928023338318</v>
       </c>
       <c r="I41" t="n">
-        <v>13.72062540054321</v>
+        <v>10.5810079574585</v>
       </c>
       <c r="J41" t="n">
-        <v>12.5926992893219</v>
+        <v>12.69115972518921</v>
       </c>
       <c r="K41" t="n">
-        <v>13.7970757484436</v>
+        <v>14.10903382301331</v>
       </c>
       <c r="L41" t="n">
-        <v>12.9816873550415</v>
+        <v>12.2125723361969</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>13.4411153793335</v>
+        <v>16.00270557403564</v>
       </c>
       <c r="C42" t="n">
-        <v>12.15633678436279</v>
+        <v>11.7353515625</v>
       </c>
       <c r="D42" t="n">
-        <v>12.84955739974976</v>
+        <v>12.929532289505</v>
       </c>
       <c r="E42" t="n">
-        <v>14.75512361526489</v>
+        <v>16.63959765434265</v>
       </c>
       <c r="F42" t="n">
-        <v>12.68219399452209</v>
+        <v>12.81836819648743</v>
       </c>
       <c r="G42" t="n">
-        <v>15.47453951835632</v>
+        <v>12.73364973068237</v>
       </c>
       <c r="H42" t="n">
-        <v>12.63978290557861</v>
+        <v>13.25526452064514</v>
       </c>
       <c r="I42" t="n">
-        <v>15.47852873802185</v>
+        <v>12.13609457015991</v>
       </c>
       <c r="J42" t="n">
-        <v>11.69666337966919</v>
+        <v>11.8507707118988</v>
       </c>
       <c r="K42" t="n">
-        <v>14.34696817398071</v>
+        <v>15.29001832008362</v>
       </c>
       <c r="L42" t="n">
-        <v>13.55208098888397</v>
+        <v>13.53913531303406</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>14.06166243553162</v>
+        <v>12.45525908470154</v>
       </c>
       <c r="C43" t="n">
-        <v>12.66967368125916</v>
+        <v>13.90609407424927</v>
       </c>
       <c r="D43" t="n">
-        <v>12.65674018859863</v>
+        <v>15.4526104927063</v>
       </c>
       <c r="E43" t="n">
-        <v>11.9824640750885</v>
+        <v>12.70513868331909</v>
       </c>
       <c r="F43" t="n">
-        <v>12.96446681022644</v>
+        <v>13.34548211097717</v>
       </c>
       <c r="G43" t="n">
-        <v>12.84624099731445</v>
+        <v>13.79234862327576</v>
       </c>
       <c r="H43" t="n">
-        <v>15.34045600891113</v>
+        <v>13.59632158279419</v>
       </c>
       <c r="I43" t="n">
-        <v>13.57939076423645</v>
+        <v>14.47009611129761</v>
       </c>
       <c r="J43" t="n">
-        <v>12.98440194129944</v>
+        <v>14.3539137840271</v>
       </c>
       <c r="K43" t="n">
-        <v>14.45114541053772</v>
+        <v>12.21185946464539</v>
       </c>
       <c r="L43" t="n">
-        <v>13.35366423130035</v>
+        <v>13.62891240119934</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>13.41379857063293</v>
+        <v>13.01186013221741</v>
       </c>
       <c r="C44" t="n">
-        <v>16.51288461685181</v>
+        <v>13.17643547058105</v>
       </c>
       <c r="D44" t="n">
-        <v>14.30806922912598</v>
+        <v>17.97069811820984</v>
       </c>
       <c r="E44" t="n">
-        <v>16.1144003868103</v>
+        <v>14.28211617469788</v>
       </c>
       <c r="F44" t="n">
-        <v>14.36788082122803</v>
+        <v>17.6929235458374</v>
       </c>
       <c r="G44" t="n">
-        <v>17.33133912086487</v>
+        <v>13.64622664451599</v>
       </c>
       <c r="H44" t="n">
-        <v>17.63207817077637</v>
+        <v>15.08706665039062</v>
       </c>
       <c r="I44" t="n">
-        <v>15.3353705406189</v>
+        <v>12.45027565956116</v>
       </c>
       <c r="J44" t="n">
-        <v>12.25673627853394</v>
+        <v>13.66827845573425</v>
       </c>
       <c r="K44" t="n">
-        <v>15.94783473014832</v>
+        <v>14.16016364097595</v>
       </c>
       <c r="L44" t="n">
-        <v>15.32203924655914</v>
+        <v>14.51460444927216</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>11.08364915847778</v>
+        <v>10.53052091598511</v>
       </c>
       <c r="C45" t="n">
-        <v>12.33241820335388</v>
+        <v>10.69075536727905</v>
       </c>
       <c r="D45" t="n">
-        <v>11.35095548629761</v>
+        <v>12.23832225799561</v>
       </c>
       <c r="E45" t="n">
-        <v>10.58349442481995</v>
+        <v>10.37705874443054</v>
       </c>
       <c r="F45" t="n">
-        <v>13.24949598312378</v>
+        <v>11.23236584663391</v>
       </c>
       <c r="G45" t="n">
-        <v>11.97826242446899</v>
+        <v>12.53254890441895</v>
       </c>
       <c r="H45" t="n">
-        <v>15.54685163497925</v>
+        <v>12.85025954246521</v>
       </c>
       <c r="I45" t="n">
-        <v>10.92165780067444</v>
+        <v>13.09013152122498</v>
       </c>
       <c r="J45" t="n">
-        <v>12.5794370174408</v>
+        <v>11.46381258964539</v>
       </c>
       <c r="K45" t="n">
-        <v>10.19199895858765</v>
+        <v>10.03943133354187</v>
       </c>
       <c r="L45" t="n">
-        <v>11.98182210922241</v>
+        <v>11.50452070236206</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>15.65640354156494</v>
+        <v>12.63480639457703</v>
       </c>
       <c r="C46" t="n">
-        <v>13.30157852172852</v>
+        <v>12.1574969291687</v>
       </c>
       <c r="D46" t="n">
-        <v>13.01091051101685</v>
+        <v>15.97674489021301</v>
       </c>
       <c r="E46" t="n">
-        <v>13.23628163337708</v>
+        <v>12.75582027435303</v>
       </c>
       <c r="F46" t="n">
-        <v>13.4966139793396</v>
+        <v>16.05321574211121</v>
       </c>
       <c r="G46" t="n">
-        <v>14.48953342437744</v>
+        <v>15.23329663276672</v>
       </c>
       <c r="H46" t="n">
-        <v>12.3240909576416</v>
+        <v>11.78081107139587</v>
       </c>
       <c r="I46" t="n">
-        <v>14.20782041549683</v>
+        <v>14.12473797798157</v>
       </c>
       <c r="J46" t="n">
-        <v>13.24422669410706</v>
+        <v>17.0346348285675</v>
       </c>
       <c r="K46" t="n">
-        <v>12.91113018989563</v>
+        <v>11.76636481285095</v>
       </c>
       <c r="L46" t="n">
-        <v>13.58785898685455</v>
+        <v>13.95179295539856</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>16.43606352806091</v>
+        <v>15.39993190765381</v>
       </c>
       <c r="C47" t="n">
-        <v>12.57943511009216</v>
+        <v>11.25172710418701</v>
       </c>
       <c r="D47" t="n">
-        <v>13.74149656295776</v>
+        <v>15.96491837501526</v>
       </c>
       <c r="E47" t="n">
-        <v>14.01928400993347</v>
+        <v>12.46361184120178</v>
       </c>
       <c r="F47" t="n">
-        <v>17.07970857620239</v>
+        <v>13.51231122016907</v>
       </c>
       <c r="G47" t="n">
-        <v>12.52589821815491</v>
+        <v>12.29650235176086</v>
       </c>
       <c r="H47" t="n">
-        <v>16.0133101940155</v>
+        <v>14.28084969520569</v>
       </c>
       <c r="I47" t="n">
-        <v>11.99177598953247</v>
+        <v>12.63860321044922</v>
       </c>
       <c r="J47" t="n">
-        <v>12.64117002487183</v>
+        <v>11.77685499191284</v>
       </c>
       <c r="K47" t="n">
-        <v>14.79853749275208</v>
+        <v>12.62114238739014</v>
       </c>
       <c r="L47" t="n">
-        <v>14.18266797065735</v>
+        <v>13.22064530849457</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>12.79221248626709</v>
+        <v>13.85901165008545</v>
       </c>
       <c r="C48" t="n">
-        <v>12.92781758308411</v>
+        <v>14.69624710083008</v>
       </c>
       <c r="D48" t="n">
-        <v>14.40152955055237</v>
+        <v>12.20768356323242</v>
       </c>
       <c r="E48" t="n">
-        <v>13.04605984687805</v>
+        <v>14.79480242729187</v>
       </c>
       <c r="F48" t="n">
-        <v>12.93979501724243</v>
+        <v>12.7061071395874</v>
       </c>
       <c r="G48" t="n">
-        <v>12.46800684928894</v>
+        <v>13.53000068664551</v>
       </c>
       <c r="H48" t="n">
-        <v>13.55725193023682</v>
+        <v>12.96794319152832</v>
       </c>
       <c r="I48" t="n">
-        <v>13.35771512985229</v>
+        <v>12.80585837364197</v>
       </c>
       <c r="J48" t="n">
-        <v>13.31284308433533</v>
+        <v>12.16900777816772</v>
       </c>
       <c r="K48" t="n">
-        <v>11.65367555618286</v>
+        <v>13.64203667640686</v>
       </c>
       <c r="L48" t="n">
-        <v>13.04569070339203</v>
+        <v>13.33786985874176</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>15.14608025550842</v>
+        <v>12.35534477233887</v>
       </c>
       <c r="C49" t="n">
-        <v>12.05667448043823</v>
+        <v>12.35682344436646</v>
       </c>
       <c r="D49" t="n">
-        <v>13.62251234054565</v>
+        <v>12.72940135002136</v>
       </c>
       <c r="E49" t="n">
-        <v>12.05962204933167</v>
+        <v>14.09032082557678</v>
       </c>
       <c r="F49" t="n">
-        <v>14.98698496818542</v>
+        <v>12.26196098327637</v>
       </c>
       <c r="G49" t="n">
-        <v>13.17521405220032</v>
+        <v>14.7668731212616</v>
       </c>
       <c r="H49" t="n">
-        <v>12.78175020217896</v>
+        <v>11.73758316040039</v>
       </c>
       <c r="I49" t="n">
-        <v>12.02118730545044</v>
+        <v>12.23945760726929</v>
       </c>
       <c r="J49" t="n">
-        <v>12.00878524780273</v>
+        <v>11.9417724609375</v>
       </c>
       <c r="K49" t="n">
-        <v>11.85463929176331</v>
+        <v>11.95006465911865</v>
       </c>
       <c r="L49" t="n">
-        <v>12.97134501934051</v>
+        <v>12.64296023845673</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>11.85514044761658</v>
+        <v>11.76748085021973</v>
       </c>
       <c r="C50" t="n">
-        <v>14.66581034660339</v>
+        <v>15.11200451850891</v>
       </c>
       <c r="D50" t="n">
-        <v>16.20983076095581</v>
+        <v>11.6204080581665</v>
       </c>
       <c r="E50" t="n">
-        <v>13.90378022193909</v>
+        <v>13.08721494674683</v>
       </c>
       <c r="F50" t="n">
-        <v>11.71102905273438</v>
+        <v>13.05373430252075</v>
       </c>
       <c r="G50" t="n">
-        <v>14.82818746566772</v>
+        <v>13.90657496452332</v>
       </c>
       <c r="H50" t="n">
-        <v>14.11102986335754</v>
+        <v>13.76343059539795</v>
       </c>
       <c r="I50" t="n">
-        <v>11.94955849647522</v>
+        <v>12.37395763397217</v>
       </c>
       <c r="J50" t="n">
-        <v>13.77042055130005</v>
+        <v>13.82478046417236</v>
       </c>
       <c r="K50" t="n">
-        <v>13.69260931015015</v>
+        <v>12.66622424125671</v>
       </c>
       <c r="L50" t="n">
-        <v>13.66973965167999</v>
+        <v>13.11758105754852</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>13.31554651260376</v>
+        <v>12.13060402870178</v>
       </c>
       <c r="C51" t="n">
-        <v>11.5261242389679</v>
+        <v>10.91371178627014</v>
       </c>
       <c r="D51" t="n">
-        <v>11.59890174865723</v>
+        <v>12.34005665779114</v>
       </c>
       <c r="E51" t="n">
-        <v>12.52258658409119</v>
+        <v>11.5894923210144</v>
       </c>
       <c r="F51" t="n">
-        <v>13.71355772018433</v>
+        <v>11.51464653015137</v>
       </c>
       <c r="G51" t="n">
-        <v>12.15250492095947</v>
+        <v>13.49310564994812</v>
       </c>
       <c r="H51" t="n">
-        <v>12.07670736312866</v>
+        <v>13.01481533050537</v>
       </c>
       <c r="I51" t="n">
-        <v>11.75053000450134</v>
+        <v>11.92112803459167</v>
       </c>
       <c r="J51" t="n">
-        <v>11.74823212623596</v>
+        <v>11.87478423118591</v>
       </c>
       <c r="K51" t="n">
-        <v>11.54236769676208</v>
+        <v>11.91614079475403</v>
       </c>
       <c r="L51" t="n">
-        <v>12.19470589160919</v>
+        <v>12.07084853649139</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>13.30643162250519</v>
+        <v>13.11759809494018</v>
       </c>
       <c r="C52" t="n">
-        <v>13.51116368770599</v>
+        <v>13.17473580360413</v>
       </c>
       <c r="D52" t="n">
-        <v>13.3676059627533</v>
+        <v>13.68145691394806</v>
       </c>
       <c r="E52" t="n">
-        <v>13.48381073951721</v>
+        <v>13.12177067279816</v>
       </c>
       <c r="F52" t="n">
-        <v>13.52418830871582</v>
+        <v>13.30969042778015</v>
       </c>
       <c r="G52" t="n">
-        <v>13.36232141971588</v>
+        <v>13.38783691883087</v>
       </c>
       <c r="H52" t="n">
-        <v>13.53706415176392</v>
+        <v>13.23109866142273</v>
       </c>
       <c r="I52" t="n">
-        <v>13.16411803245544</v>
+        <v>13.23411953449249</v>
       </c>
       <c r="J52" t="n">
-        <v>13.16517855644226</v>
+        <v>12.91832035541534</v>
       </c>
       <c r="K52" t="n">
-        <v>13.23021085262299</v>
+        <v>13.39436667919159</v>
       </c>
       <c r="L52" t="n">
-        <v>13.3652093334198</v>
+        <v>13.25709940624237</v>
       </c>
     </row>
   </sheetData>
